--- a/output/Data and Chart Outputs/chile_power_capacity.xlsx
+++ b/output/Data and Chart Outputs/chile_power_capacity.xlsx
@@ -377,7 +377,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="9A9A9A"/>
+              <a:srgbClr val="E34948"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -948,22 +948,22 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>Oil</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Bioenergy</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
           <t>Coal</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Oil</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Bioenergy</t>
-        </is>
-      </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Nuclear &amp; other</t>
         </is>
       </c>
     </row>
@@ -984,13 +984,13 @@
         <v>3.4343</v>
       </c>
       <c r="F2" t="n">
+        <v>3.3618</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.5157</v>
+      </c>
+      <c r="H2" t="n">
         <v>3.5335</v>
-      </c>
-      <c r="G2" t="n">
-        <v>3.3618</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0.5157</v>
       </c>
       <c r="I2" t="n">
         <v>0.1036</v>
@@ -1013,13 +1013,13 @@
         <v>3.5631</v>
       </c>
       <c r="F3" t="n">
+        <v>3.3704</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.5157</v>
+      </c>
+      <c r="H3" t="n">
         <v>3.5335</v>
-      </c>
-      <c r="G3" t="n">
-        <v>3.3704</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0.5157</v>
       </c>
       <c r="I3" t="n">
         <v>0.1036</v>
@@ -1042,13 +1042,13 @@
         <v>3.5657</v>
       </c>
       <c r="F4" t="n">
+        <v>3.3711</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.5157</v>
+      </c>
+      <c r="H4" t="n">
         <v>3.5335</v>
-      </c>
-      <c r="G4" t="n">
-        <v>3.3711</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.5157</v>
       </c>
       <c r="I4" t="n">
         <v>0.1036</v>
@@ -1071,13 +1071,13 @@
         <v>3.8522</v>
       </c>
       <c r="F5" t="n">
+        <v>3.3711</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.5157</v>
+      </c>
+      <c r="H5" t="n">
         <v>3.5335</v>
-      </c>
-      <c r="G5" t="n">
-        <v>3.3711</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0.5157</v>
       </c>
       <c r="I5" t="n">
         <v>0.1036</v>
@@ -1100,13 +1100,13 @@
         <v>3.8822</v>
       </c>
       <c r="F6" t="n">
+        <v>3.374</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.5157</v>
+      </c>
+      <c r="H6" t="n">
         <v>3.5335</v>
-      </c>
-      <c r="G6" t="n">
-        <v>3.374</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0.5157</v>
       </c>
       <c r="I6" t="n">
         <v>0.1036</v>
@@ -1129,13 +1129,13 @@
         <v>4.1431</v>
       </c>
       <c r="F7" t="n">
+        <v>3.383</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.5157</v>
+      </c>
+      <c r="H7" t="n">
         <v>3.5335</v>
-      </c>
-      <c r="G7" t="n">
-        <v>3.383</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0.5157</v>
       </c>
       <c r="I7" t="n">
         <v>0.1036</v>
@@ -1158,13 +1158,13 @@
         <v>4.2572</v>
       </c>
       <c r="F8" t="n">
+        <v>3.386</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.5157</v>
+      </c>
+      <c r="H8" t="n">
         <v>3.5335</v>
-      </c>
-      <c r="G8" t="n">
-        <v>3.386</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0.5157</v>
       </c>
       <c r="I8" t="n">
         <v>0.1036</v>
@@ -1187,13 +1187,13 @@
         <v>4.434699999999999</v>
       </c>
       <c r="F9" t="n">
+        <v>3.4912</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.5157</v>
+      </c>
+      <c r="H9" t="n">
         <v>3.5335</v>
-      </c>
-      <c r="G9" t="n">
-        <v>3.4912</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.5157</v>
       </c>
       <c r="I9" t="n">
         <v>0.1036</v>
@@ -1216,13 +1216,13 @@
         <v>4.583600000000001</v>
       </c>
       <c r="F10" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.5187</v>
+      </c>
+      <c r="H10" t="n">
         <v>3.5335</v>
-      </c>
-      <c r="G10" t="n">
-        <v>3.57</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0.5187</v>
       </c>
       <c r="I10" t="n">
         <v>0.1036</v>
@@ -1245,13 +1245,13 @@
         <v>4.6013</v>
       </c>
       <c r="F11" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.5187</v>
+      </c>
+      <c r="H11" t="n">
         <v>3.5335</v>
-      </c>
-      <c r="G11" t="n">
-        <v>3.57</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0.5187</v>
       </c>
       <c r="I11" t="n">
         <v>0.1036</v>
@@ -1274,13 +1274,13 @@
         <v>4.6123</v>
       </c>
       <c r="F12" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.5187</v>
+      </c>
+      <c r="H12" t="n">
         <v>3.5335</v>
-      </c>
-      <c r="G12" t="n">
-        <v>3.57</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0.5187</v>
       </c>
       <c r="I12" t="n">
         <v>0.1036</v>
@@ -1303,13 +1303,13 @@
         <v>4.8183</v>
       </c>
       <c r="F13" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.5187</v>
+      </c>
+      <c r="H13" t="n">
         <v>3.5335</v>
-      </c>
-      <c r="G13" t="n">
-        <v>3.57</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0.5187</v>
       </c>
       <c r="I13" t="n">
         <v>0.1036</v>
@@ -1332,13 +1332,13 @@
         <v>5.2668</v>
       </c>
       <c r="F14" t="n">
+        <v>3.753</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.5187</v>
+      </c>
+      <c r="H14" t="n">
         <v>3.5335</v>
-      </c>
-      <c r="G14" t="n">
-        <v>3.753</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0.5187</v>
       </c>
       <c r="I14" t="n">
         <v>0.1036</v>
@@ -1361,13 +1361,13 @@
         <v>5.2732</v>
       </c>
       <c r="F15" t="n">
+        <v>3.756</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.5187</v>
+      </c>
+      <c r="H15" t="n">
         <v>3.5335</v>
-      </c>
-      <c r="G15" t="n">
-        <v>3.756</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0.5187</v>
       </c>
       <c r="I15" t="n">
         <v>0.1036</v>
@@ -1390,13 +1390,13 @@
         <v>5.317600000000001</v>
       </c>
       <c r="F16" t="n">
+        <v>3.756</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.5187</v>
+      </c>
+      <c r="H16" t="n">
         <v>3.5335</v>
-      </c>
-      <c r="G16" t="n">
-        <v>3.756</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0.5187</v>
       </c>
       <c r="I16" t="n">
         <v>0.1036</v>
@@ -1419,13 +1419,13 @@
         <v>5.3773</v>
       </c>
       <c r="F17" t="n">
+        <v>3.759</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.5187</v>
+      </c>
+      <c r="H17" t="n">
         <v>3.5335</v>
-      </c>
-      <c r="G17" t="n">
-        <v>3.759</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0.5187</v>
       </c>
       <c r="I17" t="n">
         <v>0.1036</v>
@@ -1448,13 +1448,13 @@
         <v>5.468</v>
       </c>
       <c r="F18" t="n">
+        <v>3.7615</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.5187</v>
+      </c>
+      <c r="H18" t="n">
         <v>3.5335</v>
-      </c>
-      <c r="G18" t="n">
-        <v>3.7615</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0.5187</v>
       </c>
       <c r="I18" t="n">
         <v>0.1036</v>
@@ -1477,13 +1477,13 @@
         <v>5.5247</v>
       </c>
       <c r="F19" t="n">
+        <v>3.7615</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.5187</v>
+      </c>
+      <c r="H19" t="n">
         <v>3.5335</v>
-      </c>
-      <c r="G19" t="n">
-        <v>3.7615</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0.5187</v>
       </c>
       <c r="I19" t="n">
         <v>0.1036</v>
@@ -1506,13 +1506,13 @@
         <v>5.5679</v>
       </c>
       <c r="F20" t="n">
+        <v>3.7615</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.5187</v>
+      </c>
+      <c r="H20" t="n">
         <v>3.5335</v>
-      </c>
-      <c r="G20" t="n">
-        <v>3.7615</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0.5187</v>
       </c>
       <c r="I20" t="n">
         <v>0.1036</v>
@@ -1535,13 +1535,13 @@
         <v>5.9171</v>
       </c>
       <c r="F21" t="n">
+        <v>3.7615</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.5187</v>
+      </c>
+      <c r="H21" t="n">
         <v>3.5335</v>
-      </c>
-      <c r="G21" t="n">
-        <v>3.7615</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0.5187</v>
       </c>
       <c r="I21" t="n">
         <v>0.1036</v>
@@ -1564,13 +1564,13 @@
         <v>6.317399999999999</v>
       </c>
       <c r="F22" t="n">
+        <v>3.7615</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.5187</v>
+      </c>
+      <c r="H22" t="n">
         <v>3.5335</v>
-      </c>
-      <c r="G22" t="n">
-        <v>3.7615</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0.5187</v>
       </c>
       <c r="I22" t="n">
         <v>0.1036</v>
@@ -1593,13 +1593,13 @@
         <v>6.3521</v>
       </c>
       <c r="F23" t="n">
+        <v>3.7645</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.5187</v>
+      </c>
+      <c r="H23" t="n">
         <v>3.5335</v>
-      </c>
-      <c r="G23" t="n">
-        <v>3.7645</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0.5187</v>
       </c>
       <c r="I23" t="n">
         <v>0.1036</v>
@@ -1622,13 +1622,13 @@
         <v>6.5249</v>
       </c>
       <c r="F24" t="n">
+        <v>3.7899</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.5187</v>
+      </c>
+      <c r="H24" t="n">
         <v>3.5335</v>
-      </c>
-      <c r="G24" t="n">
-        <v>3.7899</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0.5187</v>
       </c>
       <c r="I24" t="n">
         <v>0.1036</v>
@@ -1651,13 +1651,13 @@
         <v>6.8051</v>
       </c>
       <c r="F25" t="n">
+        <v>3.7899</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.5187</v>
+      </c>
+      <c r="H25" t="n">
         <v>3.5335</v>
-      </c>
-      <c r="G25" t="n">
-        <v>3.7899</v>
-      </c>
-      <c r="H25" t="n">
-        <v>0.5187</v>
       </c>
       <c r="I25" t="n">
         <v>0.1036</v>
@@ -1680,13 +1680,13 @@
         <v>7.2185</v>
       </c>
       <c r="F26" t="n">
+        <v>3.7912</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.5187</v>
+      </c>
+      <c r="H26" t="n">
         <v>3.5335</v>
-      </c>
-      <c r="G26" t="n">
-        <v>3.7912</v>
-      </c>
-      <c r="H26" t="n">
-        <v>0.5187</v>
       </c>
       <c r="I26" t="n">
         <v>0.1036</v>
@@ -1709,13 +1709,13 @@
         <v>7.2505</v>
       </c>
       <c r="F27" t="n">
+        <v>3.7942</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0.5187</v>
+      </c>
+      <c r="H27" t="n">
         <v>3.5335</v>
-      </c>
-      <c r="G27" t="n">
-        <v>3.7942</v>
-      </c>
-      <c r="H27" t="n">
-        <v>0.5187</v>
       </c>
       <c r="I27" t="n">
         <v>0.1036</v>
@@ -1738,13 +1738,13 @@
         <v>7.489199999999999</v>
       </c>
       <c r="F28" t="n">
+        <v>3.7972</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0.5187</v>
+      </c>
+      <c r="H28" t="n">
         <v>3.5335</v>
-      </c>
-      <c r="G28" t="n">
-        <v>3.7972</v>
-      </c>
-      <c r="H28" t="n">
-        <v>0.5187</v>
       </c>
       <c r="I28" t="n">
         <v>0.1036</v>
@@ -1767,13 +1767,13 @@
         <v>7.6878</v>
       </c>
       <c r="F29" t="n">
+        <v>3.7972</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0.5187</v>
+      </c>
+      <c r="H29" t="n">
         <v>3.5335</v>
-      </c>
-      <c r="G29" t="n">
-        <v>3.7972</v>
-      </c>
-      <c r="H29" t="n">
-        <v>0.5187</v>
       </c>
       <c r="I29" t="n">
         <v>0.1036</v>
@@ -1796,13 +1796,13 @@
         <v>7.7227</v>
       </c>
       <c r="F30" t="n">
+        <v>3.7972</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0.5187</v>
+      </c>
+      <c r="H30" t="n">
         <v>3.5335</v>
-      </c>
-      <c r="G30" t="n">
-        <v>3.7972</v>
-      </c>
-      <c r="H30" t="n">
-        <v>0.5187</v>
       </c>
       <c r="I30" t="n">
         <v>0.1036</v>
@@ -1825,13 +1825,13 @@
         <v>8.115</v>
       </c>
       <c r="F31" t="n">
+        <v>3.8032</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0.5187</v>
+      </c>
+      <c r="H31" t="n">
         <v>3.5335</v>
-      </c>
-      <c r="G31" t="n">
-        <v>3.8032</v>
-      </c>
-      <c r="H31" t="n">
-        <v>0.5187</v>
       </c>
       <c r="I31" t="n">
         <v>0.1036</v>
@@ -1854,13 +1854,13 @@
         <v>8.320600000000001</v>
       </c>
       <c r="F32" t="n">
+        <v>3.8032</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0.5187</v>
+      </c>
+      <c r="H32" t="n">
         <v>3.5335</v>
-      </c>
-      <c r="G32" t="n">
-        <v>3.8032</v>
-      </c>
-      <c r="H32" t="n">
-        <v>0.5187</v>
       </c>
       <c r="I32" t="n">
         <v>0.1036</v>
@@ -1883,13 +1883,13 @@
         <v>8.379100000000001</v>
       </c>
       <c r="F33" t="n">
+        <v>3.8032</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0.5187</v>
+      </c>
+      <c r="H33" t="n">
         <v>3.5335</v>
-      </c>
-      <c r="G33" t="n">
-        <v>3.8032</v>
-      </c>
-      <c r="H33" t="n">
-        <v>0.5187</v>
       </c>
       <c r="I33" t="n">
         <v>0.1036</v>
@@ -1912,13 +1912,13 @@
         <v>8.416499999999999</v>
       </c>
       <c r="F34" t="n">
+        <v>3.8062</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0.5187</v>
+      </c>
+      <c r="H34" t="n">
         <v>3.5335</v>
-      </c>
-      <c r="G34" t="n">
-        <v>3.8062</v>
-      </c>
-      <c r="H34" t="n">
-        <v>0.5187</v>
       </c>
       <c r="I34" t="n">
         <v>0.1036</v>
@@ -1941,13 +1941,13 @@
         <v>8.464600000000001</v>
       </c>
       <c r="F35" t="n">
+        <v>3.8092</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0.5187</v>
+      </c>
+      <c r="H35" t="n">
         <v>3.5335</v>
-      </c>
-      <c r="G35" t="n">
-        <v>3.8092</v>
-      </c>
-      <c r="H35" t="n">
-        <v>0.5187</v>
       </c>
       <c r="I35" t="n">
         <v>0.1036</v>
@@ -1970,13 +1970,13 @@
         <v>8.579799999999999</v>
       </c>
       <c r="F36" t="n">
+        <v>3.877</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0.5187</v>
+      </c>
+      <c r="H36" t="n">
         <v>3.5335</v>
-      </c>
-      <c r="G36" t="n">
-        <v>3.877</v>
-      </c>
-      <c r="H36" t="n">
-        <v>0.5187</v>
       </c>
       <c r="I36" t="n">
         <v>0.1036</v>
@@ -1999,13 +1999,13 @@
         <v>8.791399999999999</v>
       </c>
       <c r="F37" t="n">
+        <v>3.877</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0.5187</v>
+      </c>
+      <c r="H37" t="n">
         <v>3.5335</v>
-      </c>
-      <c r="G37" t="n">
-        <v>3.877</v>
-      </c>
-      <c r="H37" t="n">
-        <v>0.5187</v>
       </c>
       <c r="I37" t="n">
         <v>0.1036</v>
@@ -2028,13 +2028,13 @@
         <v>9.131200000000002</v>
       </c>
       <c r="F38" t="n">
+        <v>3.877</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0.5187</v>
+      </c>
+      <c r="H38" t="n">
         <v>3.5335</v>
-      </c>
-      <c r="G38" t="n">
-        <v>3.877</v>
-      </c>
-      <c r="H38" t="n">
-        <v>0.5187</v>
       </c>
       <c r="I38" t="n">
         <v>0.1036</v>
@@ -2057,13 +2057,13 @@
         <v>9.586600000000001</v>
       </c>
       <c r="F39" t="n">
+        <v>3.877</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0.5187</v>
+      </c>
+      <c r="H39" t="n">
         <v>3.5335</v>
-      </c>
-      <c r="G39" t="n">
-        <v>3.877</v>
-      </c>
-      <c r="H39" t="n">
-        <v>0.5187</v>
       </c>
       <c r="I39" t="n">
         <v>0.1036</v>
@@ -2086,13 +2086,13 @@
         <v>9.6343</v>
       </c>
       <c r="F40" t="n">
+        <v>3.877</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0.5187</v>
+      </c>
+      <c r="H40" t="n">
         <v>3.5335</v>
-      </c>
-      <c r="G40" t="n">
-        <v>3.877</v>
-      </c>
-      <c r="H40" t="n">
-        <v>0.5187</v>
       </c>
       <c r="I40" t="n">
         <v>0.1036</v>
@@ -2115,13 +2115,13 @@
         <v>9.7165</v>
       </c>
       <c r="F41" t="n">
+        <v>3.877</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0.5187</v>
+      </c>
+      <c r="H41" t="n">
         <v>3.5335</v>
-      </c>
-      <c r="G41" t="n">
-        <v>3.877</v>
-      </c>
-      <c r="H41" t="n">
-        <v>0.5187</v>
       </c>
       <c r="I41" t="n">
         <v>0.1036</v>
@@ -2144,13 +2144,13 @@
         <v>9.765600000000001</v>
       </c>
       <c r="F42" t="n">
+        <v>3.877</v>
+      </c>
+      <c r="G42" t="n">
+        <v>0.5187</v>
+      </c>
+      <c r="H42" t="n">
         <v>3.5335</v>
-      </c>
-      <c r="G42" t="n">
-        <v>3.877</v>
-      </c>
-      <c r="H42" t="n">
-        <v>0.5187</v>
       </c>
       <c r="I42" t="n">
         <v>0.1036</v>
@@ -2173,13 +2173,13 @@
         <v>9.804799999999998</v>
       </c>
       <c r="F43" t="n">
+        <v>3.8775</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0.5187</v>
+      </c>
+      <c r="H43" t="n">
         <v>3.5335</v>
-      </c>
-      <c r="G43" t="n">
-        <v>3.8775</v>
-      </c>
-      <c r="H43" t="n">
-        <v>0.5187</v>
       </c>
       <c r="I43" t="n">
         <v>0.1036</v>
@@ -2202,13 +2202,13 @@
         <v>10.2599</v>
       </c>
       <c r="F44" t="n">
+        <v>3.8775</v>
+      </c>
+      <c r="G44" t="n">
+        <v>0.5187</v>
+      </c>
+      <c r="H44" t="n">
         <v>3.5335</v>
-      </c>
-      <c r="G44" t="n">
-        <v>3.8775</v>
-      </c>
-      <c r="H44" t="n">
-        <v>0.5187</v>
       </c>
       <c r="I44" t="n">
         <v>0.1036</v>
@@ -2231,13 +2231,13 @@
         <v>10.6244</v>
       </c>
       <c r="F45" t="n">
+        <v>3.8775</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0.5187</v>
+      </c>
+      <c r="H45" t="n">
         <v>3.5335</v>
-      </c>
-      <c r="G45" t="n">
-        <v>3.8775</v>
-      </c>
-      <c r="H45" t="n">
-        <v>0.5187</v>
       </c>
       <c r="I45" t="n">
         <v>0.1036</v>
@@ -2260,13 +2260,13 @@
         <v>10.7975</v>
       </c>
       <c r="F46" t="n">
+        <v>3.8775</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0.5187</v>
+      </c>
+      <c r="H46" t="n">
         <v>3.5335</v>
-      </c>
-      <c r="G46" t="n">
-        <v>3.8775</v>
-      </c>
-      <c r="H46" t="n">
-        <v>0.5187</v>
       </c>
       <c r="I46" t="n">
         <v>0.1036</v>
@@ -2289,13 +2289,13 @@
         <v>10.833</v>
       </c>
       <c r="F47" t="n">
+        <v>3.8775</v>
+      </c>
+      <c r="G47" t="n">
+        <v>0.5187</v>
+      </c>
+      <c r="H47" t="n">
         <v>3.5335</v>
-      </c>
-      <c r="G47" t="n">
-        <v>3.8775</v>
-      </c>
-      <c r="H47" t="n">
-        <v>0.5187</v>
       </c>
       <c r="I47" t="n">
         <v>0.1036</v>
@@ -2318,13 +2318,13 @@
         <v>10.9472</v>
       </c>
       <c r="F48" t="n">
+        <v>3.8775</v>
+      </c>
+      <c r="G48" t="n">
+        <v>0.5187</v>
+      </c>
+      <c r="H48" t="n">
         <v>3.5335</v>
-      </c>
-      <c r="G48" t="n">
-        <v>3.8775</v>
-      </c>
-      <c r="H48" t="n">
-        <v>0.5187</v>
       </c>
       <c r="I48" t="n">
         <v>0.1036</v>
@@ -2347,13 +2347,13 @@
         <v>10.9773</v>
       </c>
       <c r="F49" t="n">
+        <v>3.8775</v>
+      </c>
+      <c r="G49" t="n">
+        <v>0.5187</v>
+      </c>
+      <c r="H49" t="n">
         <v>3.5335</v>
-      </c>
-      <c r="G49" t="n">
-        <v>3.8775</v>
-      </c>
-      <c r="H49" t="n">
-        <v>0.5187</v>
       </c>
       <c r="I49" t="n">
         <v>0.1036</v>
@@ -2376,13 +2376,13 @@
         <v>11.1676</v>
       </c>
       <c r="F50" t="n">
+        <v>3.8775</v>
+      </c>
+      <c r="G50" t="n">
+        <v>0.5187</v>
+      </c>
+      <c r="H50" t="n">
         <v>3.5335</v>
-      </c>
-      <c r="G50" t="n">
-        <v>3.8775</v>
-      </c>
-      <c r="H50" t="n">
-        <v>0.5187</v>
       </c>
       <c r="I50" t="n">
         <v>0.1036</v>
@@ -2405,13 +2405,13 @@
         <v>11.2136</v>
       </c>
       <c r="F51" t="n">
+        <v>3.8775</v>
+      </c>
+      <c r="G51" t="n">
+        <v>0.5187</v>
+      </c>
+      <c r="H51" t="n">
         <v>3.5335</v>
-      </c>
-      <c r="G51" t="n">
-        <v>3.8775</v>
-      </c>
-      <c r="H51" t="n">
-        <v>0.5187</v>
       </c>
       <c r="I51" t="n">
         <v>0.1036</v>
@@ -2434,13 +2434,13 @@
         <v>11.235</v>
       </c>
       <c r="F52" t="n">
+        <v>3.8775</v>
+      </c>
+      <c r="G52" t="n">
+        <v>0.5187</v>
+      </c>
+      <c r="H52" t="n">
         <v>3.5335</v>
-      </c>
-      <c r="G52" t="n">
-        <v>3.8775</v>
-      </c>
-      <c r="H52" t="n">
-        <v>0.5187</v>
       </c>
       <c r="I52" t="n">
         <v>0.1036</v>
@@ -2463,13 +2463,13 @@
         <v>11.2785</v>
       </c>
       <c r="F53" t="n">
+        <v>3.8775</v>
+      </c>
+      <c r="G53" t="n">
+        <v>0.5187</v>
+      </c>
+      <c r="H53" t="n">
         <v>3.5335</v>
-      </c>
-      <c r="G53" t="n">
-        <v>3.8775</v>
-      </c>
-      <c r="H53" t="n">
-        <v>0.5187</v>
       </c>
       <c r="I53" t="n">
         <v>0.1036</v>
@@ -2492,13 +2492,13 @@
         <v>11.3165</v>
       </c>
       <c r="F54" t="n">
+        <v>3.8775</v>
+      </c>
+      <c r="G54" t="n">
+        <v>0.5187</v>
+      </c>
+      <c r="H54" t="n">
         <v>3.5335</v>
-      </c>
-      <c r="G54" t="n">
-        <v>3.8775</v>
-      </c>
-      <c r="H54" t="n">
-        <v>0.5187</v>
       </c>
       <c r="I54" t="n">
         <v>0.1036</v>
@@ -2521,13 +2521,13 @@
         <v>11.3714</v>
       </c>
       <c r="F55" t="n">
+        <v>3.8775</v>
+      </c>
+      <c r="G55" t="n">
+        <v>0.5187</v>
+      </c>
+      <c r="H55" t="n">
         <v>3.5335</v>
-      </c>
-      <c r="G55" t="n">
-        <v>3.8775</v>
-      </c>
-      <c r="H55" t="n">
-        <v>0.5187</v>
       </c>
       <c r="I55" t="n">
         <v>0.1036</v>
@@ -2550,13 +2550,13 @@
         <v>11.3951</v>
       </c>
       <c r="F56" t="n">
+        <v>3.8865</v>
+      </c>
+      <c r="G56" t="n">
+        <v>0.5187</v>
+      </c>
+      <c r="H56" t="n">
         <v>3.5335</v>
-      </c>
-      <c r="G56" t="n">
-        <v>3.8865</v>
-      </c>
-      <c r="H56" t="n">
-        <v>0.5187</v>
       </c>
       <c r="I56" t="n">
         <v>0.1036</v>
@@ -2579,13 +2579,13 @@
         <v>11.6151</v>
       </c>
       <c r="F57" t="n">
+        <v>3.8865</v>
+      </c>
+      <c r="G57" t="n">
+        <v>0.5187</v>
+      </c>
+      <c r="H57" t="n">
         <v>3.5335</v>
-      </c>
-      <c r="G57" t="n">
-        <v>3.8865</v>
-      </c>
-      <c r="H57" t="n">
-        <v>0.5187</v>
       </c>
       <c r="I57" t="n">
         <v>0.1036</v>
@@ -2608,13 +2608,13 @@
         <v>11.8896</v>
       </c>
       <c r="F58" t="n">
+        <v>3.8865</v>
+      </c>
+      <c r="G58" t="n">
+        <v>0.6641</v>
+      </c>
+      <c r="H58" t="n">
         <v>3.5335</v>
-      </c>
-      <c r="G58" t="n">
-        <v>3.8865</v>
-      </c>
-      <c r="H58" t="n">
-        <v>0.6641</v>
       </c>
       <c r="I58" t="n">
         <v>0.1036</v>
@@ -2637,13 +2637,13 @@
         <v>11.8986</v>
       </c>
       <c r="F59" t="n">
+        <v>3.8865</v>
+      </c>
+      <c r="G59" t="n">
+        <v>0.6641</v>
+      </c>
+      <c r="H59" t="n">
         <v>3.5335</v>
-      </c>
-      <c r="G59" t="n">
-        <v>3.8865</v>
-      </c>
-      <c r="H59" t="n">
-        <v>0.6641</v>
       </c>
       <c r="I59" t="n">
         <v>0.1036</v>
@@ -2666,13 +2666,13 @@
         <v>11.9127</v>
       </c>
       <c r="F60" t="n">
+        <v>3.8865</v>
+      </c>
+      <c r="G60" t="n">
+        <v>0.6641</v>
+      </c>
+      <c r="H60" t="n">
         <v>3.5335</v>
-      </c>
-      <c r="G60" t="n">
-        <v>3.8865</v>
-      </c>
-      <c r="H60" t="n">
-        <v>0.6641</v>
       </c>
       <c r="I60" t="n">
         <v>0.1036</v>
@@ -2695,13 +2695,13 @@
         <v>11.9608</v>
       </c>
       <c r="F61" t="n">
+        <v>3.8865</v>
+      </c>
+      <c r="G61" t="n">
+        <v>0.6641</v>
+      </c>
+      <c r="H61" t="n">
         <v>3.5335</v>
-      </c>
-      <c r="G61" t="n">
-        <v>3.8865</v>
-      </c>
-      <c r="H61" t="n">
-        <v>0.6641</v>
       </c>
       <c r="I61" t="n">
         <v>0.1036</v>
@@ -2724,13 +2724,13 @@
         <v>11.9608</v>
       </c>
       <c r="F62" t="n">
+        <v>3.8955</v>
+      </c>
+      <c r="G62" t="n">
+        <v>0.6641</v>
+      </c>
+      <c r="H62" t="n">
         <v>3.5335</v>
-      </c>
-      <c r="G62" t="n">
-        <v>3.8955</v>
-      </c>
-      <c r="H62" t="n">
-        <v>0.6641</v>
       </c>
       <c r="I62" t="n">
         <v>0.1036</v>
@@ -2753,13 +2753,13 @@
         <v>11.9758</v>
       </c>
       <c r="F63" t="n">
+        <v>3.8955</v>
+      </c>
+      <c r="G63" t="n">
+        <v>0.6641</v>
+      </c>
+      <c r="H63" t="n">
         <v>3.5335</v>
-      </c>
-      <c r="G63" t="n">
-        <v>3.8955</v>
-      </c>
-      <c r="H63" t="n">
-        <v>0.6641</v>
       </c>
       <c r="I63" t="n">
         <v>0.1036</v>
@@ -2782,13 +2782,13 @@
         <v>12.3261</v>
       </c>
       <c r="F64" t="n">
+        <v>3.8955</v>
+      </c>
+      <c r="G64" t="n">
+        <v>0.6641</v>
+      </c>
+      <c r="H64" t="n">
         <v>3.5335</v>
-      </c>
-      <c r="G64" t="n">
-        <v>3.8955</v>
-      </c>
-      <c r="H64" t="n">
-        <v>0.6641</v>
       </c>
       <c r="I64" t="n">
         <v>0.1036</v>
@@ -2811,13 +2811,13 @@
         <v>12.3345</v>
       </c>
       <c r="F65" t="n">
+        <v>3.8955</v>
+      </c>
+      <c r="G65" t="n">
+        <v>0.6641</v>
+      </c>
+      <c r="H65" t="n">
         <v>3.5335</v>
-      </c>
-      <c r="G65" t="n">
-        <v>3.8955</v>
-      </c>
-      <c r="H65" t="n">
-        <v>0.6641</v>
       </c>
       <c r="I65" t="n">
         <v>0.1036</v>
@@ -2840,13 +2840,13 @@
         <v>12.3523</v>
       </c>
       <c r="F66" t="n">
+        <v>3.8955</v>
+      </c>
+      <c r="G66" t="n">
+        <v>0.6641</v>
+      </c>
+      <c r="H66" t="n">
         <v>3.5335</v>
-      </c>
-      <c r="G66" t="n">
-        <v>3.8955</v>
-      </c>
-      <c r="H66" t="n">
-        <v>0.6641</v>
       </c>
       <c r="I66" t="n">
         <v>0.1036</v>
@@ -2869,13 +2869,13 @@
         <v>12.3782</v>
       </c>
       <c r="F67" t="n">
+        <v>3.8985</v>
+      </c>
+      <c r="G67" t="n">
+        <v>0.6641</v>
+      </c>
+      <c r="H67" t="n">
         <v>3.5335</v>
-      </c>
-      <c r="G67" t="n">
-        <v>3.8985</v>
-      </c>
-      <c r="H67" t="n">
-        <v>0.6641</v>
       </c>
       <c r="I67" t="n">
         <v>0.1036</v>
@@ -2898,13 +2898,13 @@
         <v>12.7882</v>
       </c>
       <c r="F68" t="n">
+        <v>3.8985</v>
+      </c>
+      <c r="G68" t="n">
+        <v>0.6641</v>
+      </c>
+      <c r="H68" t="n">
         <v>3.5335</v>
-      </c>
-      <c r="G68" t="n">
-        <v>3.8985</v>
-      </c>
-      <c r="H68" t="n">
-        <v>0.6641</v>
       </c>
       <c r="I68" t="n">
         <v>0.1036</v>
@@ -2927,13 +2927,13 @@
         <v>12.7882</v>
       </c>
       <c r="F69" t="n">
+        <v>3.8985</v>
+      </c>
+      <c r="G69" t="n">
+        <v>0.6641</v>
+      </c>
+      <c r="H69" t="n">
         <v>3.5335</v>
-      </c>
-      <c r="G69" t="n">
-        <v>3.8985</v>
-      </c>
-      <c r="H69" t="n">
-        <v>0.6641</v>
       </c>
       <c r="I69" t="n">
         <v>0.1036</v>

--- a/output/Data and Chart Outputs/chile_power_capacity.xlsx
+++ b/output/Data and Chart Outputs/chile_power_capacity.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Units" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Chart" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Monthly" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Coal closures (Ember)" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Fossil closures (Ember)" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="By CNE technology" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="Snapshots" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="By system (latest)" sheetId="7" state="visible" r:id="rId7"/>
@@ -841,7 +841,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>RETIREMENTS: CNE keeps only the current snapshot on cne.cl and it has no retirement dates, so months filled in on the first run (Jan 2021 to Aug 2026) count only plants still in service in Aug 2026, each from the month it entered service. Capacity retired in between (mainly coal units closed in 2021-2025, plus some diesel) is missing from the rebuild. COAL FIX: for months before Jan 2026 Coal_MW = CNE's rebuilt coal + (Ember's Chile coal capacity at the relevant year-end - Ember's end-2025 coal), so Ember's annual coal closures show while CNE's level carries on into 2026 without a step; closures are placed in December of their year (Ember is annual). Sheet 'Coal closures (Ember)' gives the adjustment by month. Other fuels are not adjusted. From the first run on, saved months are kept and only the latest two are recomputed from each new upload, so later retirements show. Battery storage is not in CNE's capacity report.</t>
+          <t>RETIREMENTS: CNE keeps only the current snapshot on cne.cl and it has no retirement dates, so months filled in on the first run (Jan 2021 to Aug 2026) count only plants still in service in Aug 2026, each from the month it entered service. Capacity retired in between (mainly coal units closed in 2021-2025, plus some diesel) is missing from the rebuild. FOSSIL FIX: for months before Jan 2026 Coal_MW, Gas_MW and Oil_MW = CNE's rebuilt MW + the part of Ember's change since end-2025 (Coal, Gas, Other Fossil) that CNE's own start dates do not explain, so retirements show and new builds are not counted twice, while CNE's level carries into 2026 without a step; changes are placed in December of their year (Ember is annual). Sheet 'Fossil closures (Ember)' gives the adjustment by month. Other fuels are not adjusted. From the first run on, saved months are kept and only the latest two are recomputed from each new upload, so later retirements show. Battery storage is not in CNE's capacity report.</t>
         </is>
       </c>
     </row>
@@ -976,7 +976,7 @@
         <v>6.6399</v>
       </c>
       <c r="C2" t="n">
-        <v>4.2553</v>
+        <v>8.5107</v>
       </c>
       <c r="D2" t="n">
         <v>2.4784</v>
@@ -985,13 +985,13 @@
         <v>3.4343</v>
       </c>
       <c r="F2" t="n">
-        <v>3.3618</v>
+        <v>6.8783</v>
       </c>
       <c r="G2" t="n">
         <v>0.5157</v>
       </c>
       <c r="H2" t="n">
-        <v>5.3535</v>
+        <v>8.887</v>
       </c>
       <c r="I2" t="n">
         <v>0.1036</v>
@@ -1005,7 +1005,7 @@
         <v>6.6399</v>
       </c>
       <c r="C3" t="n">
-        <v>4.2553</v>
+        <v>8.5107</v>
       </c>
       <c r="D3" t="n">
         <v>2.6836</v>
@@ -1014,13 +1014,13 @@
         <v>3.5631</v>
       </c>
       <c r="F3" t="n">
-        <v>3.3704</v>
+        <v>6.8869</v>
       </c>
       <c r="G3" t="n">
         <v>0.5157</v>
       </c>
       <c r="H3" t="n">
-        <v>5.3535</v>
+        <v>8.887</v>
       </c>
       <c r="I3" t="n">
         <v>0.1036</v>
@@ -1034,7 +1034,7 @@
         <v>6.6399</v>
       </c>
       <c r="C4" t="n">
-        <v>4.2553</v>
+        <v>8.5107</v>
       </c>
       <c r="D4" t="n">
         <v>2.6836</v>
@@ -1043,13 +1043,13 @@
         <v>3.5657</v>
       </c>
       <c r="F4" t="n">
-        <v>3.3711</v>
+        <v>6.8876</v>
       </c>
       <c r="G4" t="n">
         <v>0.5157</v>
       </c>
       <c r="H4" t="n">
-        <v>5.3535</v>
+        <v>8.887</v>
       </c>
       <c r="I4" t="n">
         <v>0.1036</v>
@@ -1063,7 +1063,7 @@
         <v>6.6399</v>
       </c>
       <c r="C5" t="n">
-        <v>4.2553</v>
+        <v>8.5107</v>
       </c>
       <c r="D5" t="n">
         <v>2.6836</v>
@@ -1072,13 +1072,13 @@
         <v>3.8522</v>
       </c>
       <c r="F5" t="n">
-        <v>3.3711</v>
+        <v>6.8876</v>
       </c>
       <c r="G5" t="n">
         <v>0.5157</v>
       </c>
       <c r="H5" t="n">
-        <v>5.3535</v>
+        <v>8.887</v>
       </c>
       <c r="I5" t="n">
         <v>0.1036</v>
@@ -1092,7 +1092,7 @@
         <v>6.6624</v>
       </c>
       <c r="C6" t="n">
-        <v>4.2553</v>
+        <v>8.5107</v>
       </c>
       <c r="D6" t="n">
         <v>2.6836</v>
@@ -1101,13 +1101,13 @@
         <v>3.8822</v>
       </c>
       <c r="F6" t="n">
-        <v>3.374</v>
+        <v>6.8905</v>
       </c>
       <c r="G6" t="n">
         <v>0.5157</v>
       </c>
       <c r="H6" t="n">
-        <v>5.3535</v>
+        <v>8.887</v>
       </c>
       <c r="I6" t="n">
         <v>0.1036</v>
@@ -1121,7 +1121,7 @@
         <v>6.6624</v>
       </c>
       <c r="C7" t="n">
-        <v>4.2553</v>
+        <v>8.5107</v>
       </c>
       <c r="D7" t="n">
         <v>2.7681</v>
@@ -1130,13 +1130,13 @@
         <v>4.1431</v>
       </c>
       <c r="F7" t="n">
-        <v>3.383</v>
+        <v>6.8995</v>
       </c>
       <c r="G7" t="n">
         <v>0.5157</v>
       </c>
       <c r="H7" t="n">
-        <v>5.3535</v>
+        <v>8.887</v>
       </c>
       <c r="I7" t="n">
         <v>0.1036</v>
@@ -1150,7 +1150,7 @@
         <v>6.6624</v>
       </c>
       <c r="C8" t="n">
-        <v>4.2553</v>
+        <v>8.5107</v>
       </c>
       <c r="D8" t="n">
         <v>2.7681</v>
@@ -1159,13 +1159,13 @@
         <v>4.2572</v>
       </c>
       <c r="F8" t="n">
-        <v>3.386</v>
+        <v>6.9025</v>
       </c>
       <c r="G8" t="n">
         <v>0.5157</v>
       </c>
       <c r="H8" t="n">
-        <v>5.3535</v>
+        <v>8.887</v>
       </c>
       <c r="I8" t="n">
         <v>0.1036</v>
@@ -1179,7 +1179,7 @@
         <v>6.6624</v>
       </c>
       <c r="C9" t="n">
-        <v>4.2553</v>
+        <v>8.5107</v>
       </c>
       <c r="D9" t="n">
         <v>2.7681</v>
@@ -1188,13 +1188,13 @@
         <v>4.434699999999999</v>
       </c>
       <c r="F9" t="n">
-        <v>3.4912</v>
+        <v>7.0077</v>
       </c>
       <c r="G9" t="n">
         <v>0.5157</v>
       </c>
       <c r="H9" t="n">
-        <v>5.3535</v>
+        <v>8.887</v>
       </c>
       <c r="I9" t="n">
         <v>0.1036</v>
@@ -1208,7 +1208,7 @@
         <v>6.6624</v>
       </c>
       <c r="C10" t="n">
-        <v>4.2553</v>
+        <v>8.5107</v>
       </c>
       <c r="D10" t="n">
         <v>2.8999</v>
@@ -1217,13 +1217,13 @@
         <v>4.583600000000001</v>
       </c>
       <c r="F10" t="n">
-        <v>3.57</v>
+        <v>7.0865</v>
       </c>
       <c r="G10" t="n">
         <v>0.5187</v>
       </c>
       <c r="H10" t="n">
-        <v>5.3535</v>
+        <v>8.887</v>
       </c>
       <c r="I10" t="n">
         <v>0.1036</v>
@@ -1237,7 +1237,7 @@
         <v>6.6624</v>
       </c>
       <c r="C11" t="n">
-        <v>4.2553</v>
+        <v>8.5107</v>
       </c>
       <c r="D11" t="n">
         <v>3.0606</v>
@@ -1246,13 +1246,13 @@
         <v>4.6013</v>
       </c>
       <c r="F11" t="n">
-        <v>3.57</v>
+        <v>7.0865</v>
       </c>
       <c r="G11" t="n">
         <v>0.5187</v>
       </c>
       <c r="H11" t="n">
-        <v>5.3535</v>
+        <v>8.887</v>
       </c>
       <c r="I11" t="n">
         <v>0.1036</v>
@@ -1266,7 +1266,7 @@
         <v>6.6624</v>
       </c>
       <c r="C12" t="n">
-        <v>4.2553</v>
+        <v>8.5107</v>
       </c>
       <c r="D12" t="n">
         <v>3.0606</v>
@@ -1275,13 +1275,13 @@
         <v>4.6123</v>
       </c>
       <c r="F12" t="n">
-        <v>3.57</v>
+        <v>7.0865</v>
       </c>
       <c r="G12" t="n">
         <v>0.5187</v>
       </c>
       <c r="H12" t="n">
-        <v>5.3535</v>
+        <v>8.887</v>
       </c>
       <c r="I12" t="n">
         <v>0.1036</v>
@@ -1304,7 +1304,7 @@
         <v>4.8183</v>
       </c>
       <c r="F13" t="n">
-        <v>3.57</v>
+        <v>3.8665</v>
       </c>
       <c r="G13" t="n">
         <v>0.5187</v>
@@ -1333,7 +1333,7 @@
         <v>5.2668</v>
       </c>
       <c r="F14" t="n">
-        <v>3.753</v>
+        <v>4.0494</v>
       </c>
       <c r="G14" t="n">
         <v>0.5187</v>
@@ -1362,7 +1362,7 @@
         <v>5.2732</v>
       </c>
       <c r="F15" t="n">
-        <v>3.756</v>
+        <v>4.0524</v>
       </c>
       <c r="G15" t="n">
         <v>0.5187</v>
@@ -1391,7 +1391,7 @@
         <v>5.317600000000001</v>
       </c>
       <c r="F16" t="n">
-        <v>3.756</v>
+        <v>4.0524</v>
       </c>
       <c r="G16" t="n">
         <v>0.5187</v>
@@ -1420,7 +1420,7 @@
         <v>5.3773</v>
       </c>
       <c r="F17" t="n">
-        <v>3.759</v>
+        <v>4.0554</v>
       </c>
       <c r="G17" t="n">
         <v>0.5187</v>
@@ -1449,7 +1449,7 @@
         <v>5.468</v>
       </c>
       <c r="F18" t="n">
-        <v>3.7615</v>
+        <v>4.0579</v>
       </c>
       <c r="G18" t="n">
         <v>0.5187</v>
@@ -1478,7 +1478,7 @@
         <v>5.5247</v>
       </c>
       <c r="F19" t="n">
-        <v>3.7615</v>
+        <v>4.0579</v>
       </c>
       <c r="G19" t="n">
         <v>0.5187</v>
@@ -1507,7 +1507,7 @@
         <v>5.5679</v>
       </c>
       <c r="F20" t="n">
-        <v>3.7615</v>
+        <v>4.0579</v>
       </c>
       <c r="G20" t="n">
         <v>0.5187</v>
@@ -1536,7 +1536,7 @@
         <v>5.9171</v>
       </c>
       <c r="F21" t="n">
-        <v>3.7615</v>
+        <v>4.0579</v>
       </c>
       <c r="G21" t="n">
         <v>0.5187</v>
@@ -1565,7 +1565,7 @@
         <v>6.317399999999999</v>
       </c>
       <c r="F22" t="n">
-        <v>3.7615</v>
+        <v>4.0579</v>
       </c>
       <c r="G22" t="n">
         <v>0.5187</v>
@@ -1594,7 +1594,7 @@
         <v>6.3521</v>
       </c>
       <c r="F23" t="n">
-        <v>3.7645</v>
+        <v>4.0609</v>
       </c>
       <c r="G23" t="n">
         <v>0.5187</v>
@@ -1623,7 +1623,7 @@
         <v>6.5249</v>
       </c>
       <c r="F24" t="n">
-        <v>3.7899</v>
+        <v>4.0863</v>
       </c>
       <c r="G24" t="n">
         <v>0.5187</v>
@@ -1652,7 +1652,7 @@
         <v>6.8051</v>
       </c>
       <c r="F25" t="n">
-        <v>3.7899</v>
+        <v>3.8665</v>
       </c>
       <c r="G25" t="n">
         <v>0.5187</v>
@@ -1681,7 +1681,7 @@
         <v>7.2185</v>
       </c>
       <c r="F26" t="n">
-        <v>3.7912</v>
+        <v>3.8678</v>
       </c>
       <c r="G26" t="n">
         <v>0.5187</v>
@@ -1710,7 +1710,7 @@
         <v>7.2505</v>
       </c>
       <c r="F27" t="n">
-        <v>3.7942</v>
+        <v>3.8708</v>
       </c>
       <c r="G27" t="n">
         <v>0.5187</v>
@@ -1739,7 +1739,7 @@
         <v>7.489199999999999</v>
       </c>
       <c r="F28" t="n">
-        <v>3.7972</v>
+        <v>3.8738</v>
       </c>
       <c r="G28" t="n">
         <v>0.5187</v>
@@ -1768,7 +1768,7 @@
         <v>7.6878</v>
       </c>
       <c r="F29" t="n">
-        <v>3.7972</v>
+        <v>3.8738</v>
       </c>
       <c r="G29" t="n">
         <v>0.5187</v>
@@ -1797,7 +1797,7 @@
         <v>7.7227</v>
       </c>
       <c r="F30" t="n">
-        <v>3.7972</v>
+        <v>3.8738</v>
       </c>
       <c r="G30" t="n">
         <v>0.5187</v>
@@ -1826,7 +1826,7 @@
         <v>8.115</v>
       </c>
       <c r="F31" t="n">
-        <v>3.8032</v>
+        <v>3.8798</v>
       </c>
       <c r="G31" t="n">
         <v>0.5187</v>
@@ -1855,7 +1855,7 @@
         <v>8.320600000000001</v>
       </c>
       <c r="F32" t="n">
-        <v>3.8032</v>
+        <v>3.8798</v>
       </c>
       <c r="G32" t="n">
         <v>0.5187</v>
@@ -1884,7 +1884,7 @@
         <v>8.379100000000001</v>
       </c>
       <c r="F33" t="n">
-        <v>3.8032</v>
+        <v>3.8798</v>
       </c>
       <c r="G33" t="n">
         <v>0.5187</v>
@@ -1913,7 +1913,7 @@
         <v>8.416499999999999</v>
       </c>
       <c r="F34" t="n">
-        <v>3.8062</v>
+        <v>3.8828</v>
       </c>
       <c r="G34" t="n">
         <v>0.5187</v>
@@ -1942,7 +1942,7 @@
         <v>8.464600000000001</v>
       </c>
       <c r="F35" t="n">
-        <v>3.8092</v>
+        <v>3.8858</v>
       </c>
       <c r="G35" t="n">
         <v>0.5187</v>
@@ -1971,7 +1971,7 @@
         <v>8.579799999999999</v>
       </c>
       <c r="F36" t="n">
-        <v>3.877</v>
+        <v>3.9536</v>
       </c>
       <c r="G36" t="n">
         <v>0.5187</v>
@@ -2000,7 +2000,7 @@
         <v>8.791399999999999</v>
       </c>
       <c r="F37" t="n">
-        <v>3.877</v>
+        <v>3.8165</v>
       </c>
       <c r="G37" t="n">
         <v>0.5187</v>
@@ -2029,7 +2029,7 @@
         <v>9.131200000000002</v>
       </c>
       <c r="F38" t="n">
-        <v>3.877</v>
+        <v>3.8165</v>
       </c>
       <c r="G38" t="n">
         <v>0.5187</v>
@@ -2058,7 +2058,7 @@
         <v>9.586600000000001</v>
       </c>
       <c r="F39" t="n">
-        <v>3.877</v>
+        <v>3.8165</v>
       </c>
       <c r="G39" t="n">
         <v>0.5187</v>
@@ -2087,7 +2087,7 @@
         <v>9.6343</v>
       </c>
       <c r="F40" t="n">
-        <v>3.877</v>
+        <v>3.8165</v>
       </c>
       <c r="G40" t="n">
         <v>0.5187</v>
@@ -2116,7 +2116,7 @@
         <v>9.7165</v>
       </c>
       <c r="F41" t="n">
-        <v>3.877</v>
+        <v>3.8165</v>
       </c>
       <c r="G41" t="n">
         <v>0.5187</v>
@@ -2145,7 +2145,7 @@
         <v>9.765600000000001</v>
       </c>
       <c r="F42" t="n">
-        <v>3.877</v>
+        <v>3.8165</v>
       </c>
       <c r="G42" t="n">
         <v>0.5187</v>
@@ -2174,7 +2174,7 @@
         <v>9.804799999999998</v>
       </c>
       <c r="F43" t="n">
-        <v>3.8775</v>
+        <v>3.817</v>
       </c>
       <c r="G43" t="n">
         <v>0.5187</v>
@@ -2203,7 +2203,7 @@
         <v>10.2599</v>
       </c>
       <c r="F44" t="n">
-        <v>3.8775</v>
+        <v>3.817</v>
       </c>
       <c r="G44" t="n">
         <v>0.5187</v>
@@ -2232,7 +2232,7 @@
         <v>10.6244</v>
       </c>
       <c r="F45" t="n">
-        <v>3.8775</v>
+        <v>3.817</v>
       </c>
       <c r="G45" t="n">
         <v>0.5187</v>
@@ -2261,7 +2261,7 @@
         <v>10.7975</v>
       </c>
       <c r="F46" t="n">
-        <v>3.8775</v>
+        <v>3.817</v>
       </c>
       <c r="G46" t="n">
         <v>0.5187</v>
@@ -2290,7 +2290,7 @@
         <v>10.833</v>
       </c>
       <c r="F47" t="n">
-        <v>3.8775</v>
+        <v>3.817</v>
       </c>
       <c r="G47" t="n">
         <v>0.5187</v>
@@ -2319,7 +2319,7 @@
         <v>10.9472</v>
       </c>
       <c r="F48" t="n">
-        <v>3.8775</v>
+        <v>3.817</v>
       </c>
       <c r="G48" t="n">
         <v>0.5187</v>
@@ -2348,7 +2348,7 @@
         <v>10.9773</v>
       </c>
       <c r="F49" t="n">
-        <v>3.8775</v>
+        <v>3.8865</v>
       </c>
       <c r="G49" t="n">
         <v>0.5187</v>
@@ -2377,7 +2377,7 @@
         <v>11.1676</v>
       </c>
       <c r="F50" t="n">
-        <v>3.8775</v>
+        <v>3.8865</v>
       </c>
       <c r="G50" t="n">
         <v>0.5187</v>
@@ -2406,7 +2406,7 @@
         <v>11.2136</v>
       </c>
       <c r="F51" t="n">
-        <v>3.8775</v>
+        <v>3.8865</v>
       </c>
       <c r="G51" t="n">
         <v>0.5187</v>
@@ -2435,7 +2435,7 @@
         <v>11.235</v>
       </c>
       <c r="F52" t="n">
-        <v>3.8775</v>
+        <v>3.8865</v>
       </c>
       <c r="G52" t="n">
         <v>0.5187</v>
@@ -2464,7 +2464,7 @@
         <v>11.2785</v>
       </c>
       <c r="F53" t="n">
-        <v>3.8775</v>
+        <v>3.8865</v>
       </c>
       <c r="G53" t="n">
         <v>0.5187</v>
@@ -2493,7 +2493,7 @@
         <v>11.3165</v>
       </c>
       <c r="F54" t="n">
-        <v>3.8775</v>
+        <v>3.8865</v>
       </c>
       <c r="G54" t="n">
         <v>0.5187</v>
@@ -2522,7 +2522,7 @@
         <v>11.3714</v>
       </c>
       <c r="F55" t="n">
-        <v>3.8775</v>
+        <v>3.8865</v>
       </c>
       <c r="G55" t="n">
         <v>0.5187</v>
@@ -2551,7 +2551,7 @@
         <v>11.3951</v>
       </c>
       <c r="F56" t="n">
-        <v>3.8865</v>
+        <v>3.8955</v>
       </c>
       <c r="G56" t="n">
         <v>0.5187</v>
@@ -2580,7 +2580,7 @@
         <v>11.6151</v>
       </c>
       <c r="F57" t="n">
-        <v>3.8865</v>
+        <v>3.8955</v>
       </c>
       <c r="G57" t="n">
         <v>0.5187</v>
@@ -2609,7 +2609,7 @@
         <v>11.8896</v>
       </c>
       <c r="F58" t="n">
-        <v>3.8865</v>
+        <v>3.8955</v>
       </c>
       <c r="G58" t="n">
         <v>0.6641</v>
@@ -2638,7 +2638,7 @@
         <v>11.8986</v>
       </c>
       <c r="F59" t="n">
-        <v>3.8865</v>
+        <v>3.8955</v>
       </c>
       <c r="G59" t="n">
         <v>0.6641</v>
@@ -2667,7 +2667,7 @@
         <v>11.9127</v>
       </c>
       <c r="F60" t="n">
-        <v>3.8865</v>
+        <v>3.8955</v>
       </c>
       <c r="G60" t="n">
         <v>0.6641</v>
@@ -3020,7 +3020,7 @@
         <v>6639.9</v>
       </c>
       <c r="C2" t="n">
-        <v>4255.3</v>
+        <v>8510.700000000001</v>
       </c>
       <c r="D2" t="n">
         <v>2478.4</v>
@@ -3029,13 +3029,13 @@
         <v>3434.3</v>
       </c>
       <c r="F2" t="n">
-        <v>5353.5</v>
+        <v>8887</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>3361.8</v>
+        <v>6878.3</v>
       </c>
       <c r="I2" t="n">
         <v>515.7</v>
@@ -3044,7 +3044,7 @@
         <v>103.6</v>
       </c>
       <c r="K2" t="n">
-        <v>26142.5</v>
+        <v>37447.9</v>
       </c>
     </row>
     <row r="3">
@@ -3055,7 +3055,7 @@
         <v>6639.9</v>
       </c>
       <c r="C3" t="n">
-        <v>4255.3</v>
+        <v>8510.700000000001</v>
       </c>
       <c r="D3" t="n">
         <v>2683.6</v>
@@ -3064,13 +3064,13 @@
         <v>3563.1</v>
       </c>
       <c r="F3" t="n">
-        <v>5353.5</v>
+        <v>8887</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>3370.4</v>
+        <v>6886.9</v>
       </c>
       <c r="I3" t="n">
         <v>515.7</v>
@@ -3079,7 +3079,7 @@
         <v>103.6</v>
       </c>
       <c r="K3" t="n">
-        <v>26485.1</v>
+        <v>37790.5</v>
       </c>
     </row>
     <row r="4">
@@ -3090,7 +3090,7 @@
         <v>6639.9</v>
       </c>
       <c r="C4" t="n">
-        <v>4255.3</v>
+        <v>8510.700000000001</v>
       </c>
       <c r="D4" t="n">
         <v>2683.6</v>
@@ -3099,13 +3099,13 @@
         <v>3565.7</v>
       </c>
       <c r="F4" t="n">
-        <v>5353.5</v>
+        <v>8887</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>3371.1</v>
+        <v>6887.6</v>
       </c>
       <c r="I4" t="n">
         <v>515.7</v>
@@ -3114,7 +3114,7 @@
         <v>103.6</v>
       </c>
       <c r="K4" t="n">
-        <v>26488.4</v>
+        <v>37793.8</v>
       </c>
     </row>
     <row r="5">
@@ -3125,7 +3125,7 @@
         <v>6639.9</v>
       </c>
       <c r="C5" t="n">
-        <v>4255.3</v>
+        <v>8510.700000000001</v>
       </c>
       <c r="D5" t="n">
         <v>2683.6</v>
@@ -3134,13 +3134,13 @@
         <v>3852.2</v>
       </c>
       <c r="F5" t="n">
-        <v>5353.5</v>
+        <v>8887</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>3371.1</v>
+        <v>6887.6</v>
       </c>
       <c r="I5" t="n">
         <v>515.7</v>
@@ -3149,7 +3149,7 @@
         <v>103.6</v>
       </c>
       <c r="K5" t="n">
-        <v>26774.9</v>
+        <v>38080.3</v>
       </c>
     </row>
     <row r="6">
@@ -3160,7 +3160,7 @@
         <v>6662.4</v>
       </c>
       <c r="C6" t="n">
-        <v>4255.3</v>
+        <v>8510.700000000001</v>
       </c>
       <c r="D6" t="n">
         <v>2683.6</v>
@@ -3169,13 +3169,13 @@
         <v>3882.2</v>
       </c>
       <c r="F6" t="n">
-        <v>5353.5</v>
+        <v>8887</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>3374</v>
+        <v>6890.5</v>
       </c>
       <c r="I6" t="n">
         <v>515.7</v>
@@ -3184,7 +3184,7 @@
         <v>103.6</v>
       </c>
       <c r="K6" t="n">
-        <v>26830.3</v>
+        <v>38135.7</v>
       </c>
     </row>
     <row r="7">
@@ -3195,7 +3195,7 @@
         <v>6662.4</v>
       </c>
       <c r="C7" t="n">
-        <v>4255.3</v>
+        <v>8510.700000000001</v>
       </c>
       <c r="D7" t="n">
         <v>2768.1</v>
@@ -3204,13 +3204,13 @@
         <v>4143.1</v>
       </c>
       <c r="F7" t="n">
-        <v>5353.5</v>
+        <v>8887</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>3383</v>
+        <v>6899.5</v>
       </c>
       <c r="I7" t="n">
         <v>515.7</v>
@@ -3219,7 +3219,7 @@
         <v>103.6</v>
       </c>
       <c r="K7" t="n">
-        <v>27184.7</v>
+        <v>38490.1</v>
       </c>
     </row>
     <row r="8">
@@ -3230,7 +3230,7 @@
         <v>6662.4</v>
       </c>
       <c r="C8" t="n">
-        <v>4255.3</v>
+        <v>8510.700000000001</v>
       </c>
       <c r="D8" t="n">
         <v>2768.1</v>
@@ -3239,13 +3239,13 @@
         <v>4257.2</v>
       </c>
       <c r="F8" t="n">
-        <v>5353.5</v>
+        <v>8887</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>3386</v>
+        <v>6902.5</v>
       </c>
       <c r="I8" t="n">
         <v>515.7</v>
@@ -3254,7 +3254,7 @@
         <v>103.6</v>
       </c>
       <c r="K8" t="n">
-        <v>27301.8</v>
+        <v>38607.2</v>
       </c>
     </row>
     <row r="9">
@@ -3265,7 +3265,7 @@
         <v>6662.4</v>
       </c>
       <c r="C9" t="n">
-        <v>4255.3</v>
+        <v>8510.700000000001</v>
       </c>
       <c r="D9" t="n">
         <v>2768.1</v>
@@ -3274,13 +3274,13 @@
         <v>4434.7</v>
       </c>
       <c r="F9" t="n">
-        <v>5353.5</v>
+        <v>8887</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>3491.2</v>
+        <v>7007.7</v>
       </c>
       <c r="I9" t="n">
         <v>515.7</v>
@@ -3289,7 +3289,7 @@
         <v>103.6</v>
       </c>
       <c r="K9" t="n">
-        <v>27584.5</v>
+        <v>38889.9</v>
       </c>
     </row>
     <row r="10">
@@ -3300,7 +3300,7 @@
         <v>6662.4</v>
       </c>
       <c r="C10" t="n">
-        <v>4255.3</v>
+        <v>8510.700000000001</v>
       </c>
       <c r="D10" t="n">
         <v>2899.9</v>
@@ -3309,13 +3309,13 @@
         <v>4583.6</v>
       </c>
       <c r="F10" t="n">
-        <v>5353.5</v>
+        <v>8887</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>3570</v>
+        <v>7086.5</v>
       </c>
       <c r="I10" t="n">
         <v>518.7</v>
@@ -3324,7 +3324,7 @@
         <v>103.6</v>
       </c>
       <c r="K10" t="n">
-        <v>27947</v>
+        <v>39252.4</v>
       </c>
     </row>
     <row r="11">
@@ -3335,7 +3335,7 @@
         <v>6662.4</v>
       </c>
       <c r="C11" t="n">
-        <v>4255.3</v>
+        <v>8510.700000000001</v>
       </c>
       <c r="D11" t="n">
         <v>3060.6</v>
@@ -3344,13 +3344,13 @@
         <v>4601.3</v>
       </c>
       <c r="F11" t="n">
-        <v>5353.5</v>
+        <v>8887</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>3570</v>
+        <v>7086.5</v>
       </c>
       <c r="I11" t="n">
         <v>518.7</v>
@@ -3359,7 +3359,7 @@
         <v>103.6</v>
       </c>
       <c r="K11" t="n">
-        <v>28125.4</v>
+        <v>39430.8</v>
       </c>
     </row>
     <row r="12">
@@ -3370,7 +3370,7 @@
         <v>6662.4</v>
       </c>
       <c r="C12" t="n">
-        <v>4255.3</v>
+        <v>8510.700000000001</v>
       </c>
       <c r="D12" t="n">
         <v>3060.6</v>
@@ -3379,13 +3379,13 @@
         <v>4612.3</v>
       </c>
       <c r="F12" t="n">
-        <v>5353.5</v>
+        <v>8887</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>3570</v>
+        <v>7086.5</v>
       </c>
       <c r="I12" t="n">
         <v>518.7</v>
@@ -3394,7 +3394,7 @@
         <v>103.6</v>
       </c>
       <c r="K12" t="n">
-        <v>28136.4</v>
+        <v>39441.8</v>
       </c>
     </row>
     <row r="13">
@@ -3420,7 +3420,7 @@
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>3570</v>
+        <v>3866.5</v>
       </c>
       <c r="I13" t="n">
         <v>518.7</v>
@@ -3429,7 +3429,7 @@
         <v>103.6</v>
       </c>
       <c r="K13" t="n">
-        <v>28426.4</v>
+        <v>28722.9</v>
       </c>
     </row>
     <row r="14">
@@ -3455,7 +3455,7 @@
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>3753</v>
+        <v>4049.4</v>
       </c>
       <c r="I14" t="n">
         <v>518.7</v>
@@ -3464,7 +3464,7 @@
         <v>103.6</v>
       </c>
       <c r="K14" t="n">
-        <v>29173.8</v>
+        <v>29470.2</v>
       </c>
     </row>
     <row r="15">
@@ -3490,7 +3490,7 @@
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>3756</v>
+        <v>4052.4</v>
       </c>
       <c r="I15" t="n">
         <v>518.7</v>
@@ -3499,7 +3499,7 @@
         <v>103.6</v>
       </c>
       <c r="K15" t="n">
-        <v>29488.9</v>
+        <v>29785.3</v>
       </c>
     </row>
     <row r="16">
@@ -3525,7 +3525,7 @@
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>3756</v>
+        <v>4052.4</v>
       </c>
       <c r="I16" t="n">
         <v>518.7</v>
@@ -3534,7 +3534,7 @@
         <v>103.6</v>
       </c>
       <c r="K16" t="n">
-        <v>30252.1</v>
+        <v>30548.5</v>
       </c>
     </row>
     <row r="17">
@@ -3560,7 +3560,7 @@
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>3759</v>
+        <v>4055.4</v>
       </c>
       <c r="I17" t="n">
         <v>518.7</v>
@@ -3569,7 +3569,7 @@
         <v>103.6</v>
       </c>
       <c r="K17" t="n">
-        <v>30314.8</v>
+        <v>30611.2</v>
       </c>
     </row>
     <row r="18">
@@ -3595,7 +3595,7 @@
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>3761.5</v>
+        <v>4057.9</v>
       </c>
       <c r="I18" t="n">
         <v>518.7</v>
@@ -3604,7 +3604,7 @@
         <v>103.6</v>
       </c>
       <c r="K18" t="n">
-        <v>30408.2</v>
+        <v>30704.6</v>
       </c>
     </row>
     <row r="19">
@@ -3630,7 +3630,7 @@
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>3761.5</v>
+        <v>4057.9</v>
       </c>
       <c r="I19" t="n">
         <v>518.7</v>
@@ -3639,7 +3639,7 @@
         <v>103.6</v>
       </c>
       <c r="K19" t="n">
-        <v>30464.9</v>
+        <v>30761.3</v>
       </c>
     </row>
     <row r="20">
@@ -3665,7 +3665,7 @@
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>3761.5</v>
+        <v>4057.9</v>
       </c>
       <c r="I20" t="n">
         <v>518.7</v>
@@ -3674,7 +3674,7 @@
         <v>103.6</v>
       </c>
       <c r="K20" t="n">
-        <v>30568.1</v>
+        <v>30864.5</v>
       </c>
     </row>
     <row r="21">
@@ -3700,7 +3700,7 @@
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>3761.5</v>
+        <v>4057.9</v>
       </c>
       <c r="I21" t="n">
         <v>518.7</v>
@@ -3709,7 +3709,7 @@
         <v>103.6</v>
       </c>
       <c r="K21" t="n">
-        <v>30978.3</v>
+        <v>31274.7</v>
       </c>
     </row>
     <row r="22">
@@ -3735,7 +3735,7 @@
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>3761.5</v>
+        <v>4057.9</v>
       </c>
       <c r="I22" t="n">
         <v>518.7</v>
@@ -3744,7 +3744,7 @@
         <v>103.6</v>
       </c>
       <c r="K22" t="n">
-        <v>31378.6</v>
+        <v>31675</v>
       </c>
     </row>
     <row r="23">
@@ -3770,7 +3770,7 @@
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>3764.5</v>
+        <v>4060.9</v>
       </c>
       <c r="I23" t="n">
         <v>518.7</v>
@@ -3779,7 +3779,7 @@
         <v>103.6</v>
       </c>
       <c r="K23" t="n">
-        <v>31416.3</v>
+        <v>31712.7</v>
       </c>
     </row>
     <row r="24">
@@ -3805,7 +3805,7 @@
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>3789.9</v>
+        <v>4086.3</v>
       </c>
       <c r="I24" t="n">
         <v>518.7</v>
@@ -3814,7 +3814,7 @@
         <v>103.6</v>
       </c>
       <c r="K24" t="n">
-        <v>31625.9</v>
+        <v>31922.3</v>
       </c>
     </row>
     <row r="25">
@@ -3840,7 +3840,7 @@
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>3789.9</v>
+        <v>3866.5</v>
       </c>
       <c r="I25" t="n">
         <v>518.7</v>
@@ -3849,7 +3849,7 @@
         <v>103.6</v>
       </c>
       <c r="K25" t="n">
-        <v>31286.1</v>
+        <v>31362.7</v>
       </c>
     </row>
     <row r="26">
@@ -3875,7 +3875,7 @@
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>3791.2</v>
+        <v>3867.8</v>
       </c>
       <c r="I26" t="n">
         <v>518.7</v>
@@ -3884,7 +3884,7 @@
         <v>103.6</v>
       </c>
       <c r="K26" t="n">
-        <v>31859.9</v>
+        <v>31936.5</v>
       </c>
     </row>
     <row r="27">
@@ -3910,7 +3910,7 @@
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>3794.2</v>
+        <v>3870.8</v>
       </c>
       <c r="I27" t="n">
         <v>518.7</v>
@@ -3919,7 +3919,7 @@
         <v>103.6</v>
       </c>
       <c r="K27" t="n">
-        <v>31894.9</v>
+        <v>31971.5</v>
       </c>
     </row>
     <row r="28">
@@ -3945,7 +3945,7 @@
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>3797.2</v>
+        <v>3873.8</v>
       </c>
       <c r="I28" t="n">
         <v>518.7</v>
@@ -3954,7 +3954,7 @@
         <v>103.6</v>
       </c>
       <c r="K28" t="n">
-        <v>32304</v>
+        <v>32380.6</v>
       </c>
     </row>
     <row r="29">
@@ -3980,7 +3980,7 @@
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>3797.2</v>
+        <v>3873.8</v>
       </c>
       <c r="I29" t="n">
         <v>518.7</v>
@@ -3989,7 +3989,7 @@
         <v>103.6</v>
       </c>
       <c r="K29" t="n">
-        <v>32565.5</v>
+        <v>32642.1</v>
       </c>
     </row>
     <row r="30">
@@ -4015,7 +4015,7 @@
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>3797.2</v>
+        <v>3873.8</v>
       </c>
       <c r="I30" t="n">
         <v>518.7</v>
@@ -4024,7 +4024,7 @@
         <v>103.6</v>
       </c>
       <c r="K30" t="n">
-        <v>32600.4</v>
+        <v>32677</v>
       </c>
     </row>
     <row r="31">
@@ -4050,7 +4050,7 @@
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>3803.2</v>
+        <v>3879.8</v>
       </c>
       <c r="I31" t="n">
         <v>518.7</v>
@@ -4059,7 +4059,7 @@
         <v>103.6</v>
       </c>
       <c r="K31" t="n">
-        <v>33005.5</v>
+        <v>33082.1</v>
       </c>
     </row>
     <row r="32">
@@ -4085,7 +4085,7 @@
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>3803.2</v>
+        <v>3879.8</v>
       </c>
       <c r="I32" t="n">
         <v>518.7</v>
@@ -4094,7 +4094,7 @@
         <v>103.6</v>
       </c>
       <c r="K32" t="n">
-        <v>33211.1</v>
+        <v>33287.7</v>
       </c>
     </row>
     <row r="33">
@@ -4120,7 +4120,7 @@
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>3803.2</v>
+        <v>3879.8</v>
       </c>
       <c r="I33" t="n">
         <v>518.7</v>
@@ -4129,7 +4129,7 @@
         <v>103.6</v>
       </c>
       <c r="K33" t="n">
-        <v>33411</v>
+        <v>33487.6</v>
       </c>
     </row>
     <row r="34">
@@ -4155,7 +4155,7 @@
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>3806.2</v>
+        <v>3882.8</v>
       </c>
       <c r="I34" t="n">
         <v>518.7</v>
@@ -4164,7 +4164,7 @@
         <v>103.6</v>
       </c>
       <c r="K34" t="n">
-        <v>33611.7</v>
+        <v>33688.3</v>
       </c>
     </row>
     <row r="35">
@@ -4190,7 +4190,7 @@
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>3809.2</v>
+        <v>3885.8</v>
       </c>
       <c r="I35" t="n">
         <v>518.7</v>
@@ -4199,7 +4199,7 @@
         <v>103.6</v>
       </c>
       <c r="K35" t="n">
-        <v>33662.8</v>
+        <v>33739.4</v>
       </c>
     </row>
     <row r="36">
@@ -4225,7 +4225,7 @@
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>3877</v>
+        <v>3953.6</v>
       </c>
       <c r="I36" t="n">
         <v>518.7</v>
@@ -4234,7 +4234,7 @@
         <v>103.6</v>
       </c>
       <c r="K36" t="n">
-        <v>33845.8</v>
+        <v>33922.4</v>
       </c>
     </row>
     <row r="37">
@@ -4260,7 +4260,7 @@
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>3877</v>
+        <v>3816.5</v>
       </c>
       <c r="I37" t="n">
         <v>518.7</v>
@@ -4269,7 +4269,7 @@
         <v>103.6</v>
       </c>
       <c r="K37" t="n">
-        <v>33839.3</v>
+        <v>33778.8</v>
       </c>
     </row>
     <row r="38">
@@ -4295,7 +4295,7 @@
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>3877</v>
+        <v>3816.5</v>
       </c>
       <c r="I38" t="n">
         <v>518.7</v>
@@ -4304,7 +4304,7 @@
         <v>103.6</v>
       </c>
       <c r="K38" t="n">
-        <v>34179.1</v>
+        <v>34118.6</v>
       </c>
     </row>
     <row r="39">
@@ -4330,7 +4330,7 @@
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>3877</v>
+        <v>3816.5</v>
       </c>
       <c r="I39" t="n">
         <v>518.7</v>
@@ -4339,7 +4339,7 @@
         <v>103.6</v>
       </c>
       <c r="K39" t="n">
-        <v>34683.5</v>
+        <v>34623</v>
       </c>
     </row>
     <row r="40">
@@ -4365,7 +4365,7 @@
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>3877</v>
+        <v>3816.5</v>
       </c>
       <c r="I40" t="n">
         <v>518.7</v>
@@ -4374,7 +4374,7 @@
         <v>103.6</v>
       </c>
       <c r="K40" t="n">
-        <v>34732.3</v>
+        <v>34671.8</v>
       </c>
     </row>
     <row r="41">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>3877</v>
+        <v>3816.5</v>
       </c>
       <c r="I41" t="n">
         <v>518.7</v>
@@ -4409,7 +4409,7 @@
         <v>103.6</v>
       </c>
       <c r="K41" t="n">
-        <v>34814.5</v>
+        <v>34754</v>
       </c>
     </row>
     <row r="42">
@@ -4435,7 +4435,7 @@
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>3877</v>
+        <v>3816.5</v>
       </c>
       <c r="I42" t="n">
         <v>518.7</v>
@@ -4444,7 +4444,7 @@
         <v>103.6</v>
       </c>
       <c r="K42" t="n">
-        <v>34863.6</v>
+        <v>34803.1</v>
       </c>
     </row>
     <row r="43">
@@ -4470,7 +4470,7 @@
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>3877.5</v>
+        <v>3817</v>
       </c>
       <c r="I43" t="n">
         <v>518.7</v>
@@ -4479,7 +4479,7 @@
         <v>103.6</v>
       </c>
       <c r="K43" t="n">
-        <v>35013.7</v>
+        <v>34953.2</v>
       </c>
     </row>
     <row r="44">
@@ -4505,7 +4505,7 @@
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>3877.5</v>
+        <v>3817</v>
       </c>
       <c r="I44" t="n">
         <v>518.7</v>
@@ -4514,7 +4514,7 @@
         <v>103.6</v>
       </c>
       <c r="K44" t="n">
-        <v>35468.8</v>
+        <v>35408.3</v>
       </c>
     </row>
     <row r="45">
@@ -4540,7 +4540,7 @@
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>3877.5</v>
+        <v>3817</v>
       </c>
       <c r="I45" t="n">
         <v>518.7</v>
@@ -4549,7 +4549,7 @@
         <v>103.6</v>
       </c>
       <c r="K45" t="n">
-        <v>35904.4</v>
+        <v>35843.9</v>
       </c>
     </row>
     <row r="46">
@@ -4575,7 +4575,7 @@
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>3877.5</v>
+        <v>3817</v>
       </c>
       <c r="I46" t="n">
         <v>518.7</v>
@@ -4584,7 +4584,7 @@
         <v>103.6</v>
       </c>
       <c r="K46" t="n">
-        <v>36077.5</v>
+        <v>36017</v>
       </c>
     </row>
     <row r="47">
@@ -4610,7 +4610,7 @@
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>3877.5</v>
+        <v>3817</v>
       </c>
       <c r="I47" t="n">
         <v>518.7</v>
@@ -4619,7 +4619,7 @@
         <v>103.6</v>
       </c>
       <c r="K47" t="n">
-        <v>36115.9</v>
+        <v>36055.4</v>
       </c>
     </row>
     <row r="48">
@@ -4645,7 +4645,7 @@
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>3877.5</v>
+        <v>3817</v>
       </c>
       <c r="I48" t="n">
         <v>518.7</v>
@@ -4654,7 +4654,7 @@
         <v>103.6</v>
       </c>
       <c r="K48" t="n">
-        <v>36230.1</v>
+        <v>36169.6</v>
       </c>
     </row>
     <row r="49">
@@ -4680,7 +4680,7 @@
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>3877.5</v>
+        <v>3886.5</v>
       </c>
       <c r="I49" t="n">
         <v>518.7</v>
@@ -4689,7 +4689,7 @@
         <v>103.6</v>
       </c>
       <c r="K49" t="n">
-        <v>35990.2</v>
+        <v>35999.2</v>
       </c>
     </row>
     <row r="50">
@@ -4715,7 +4715,7 @@
         <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>3877.5</v>
+        <v>3886.5</v>
       </c>
       <c r="I50" t="n">
         <v>518.7</v>
@@ -4724,7 +4724,7 @@
         <v>103.6</v>
       </c>
       <c r="K50" t="n">
-        <v>36180.5</v>
+        <v>36189.5</v>
       </c>
     </row>
     <row r="51">
@@ -4750,7 +4750,7 @@
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>3877.5</v>
+        <v>3886.5</v>
       </c>
       <c r="I51" t="n">
         <v>518.7</v>
@@ -4759,7 +4759,7 @@
         <v>103.6</v>
       </c>
       <c r="K51" t="n">
-        <v>36396.3</v>
+        <v>36405.3</v>
       </c>
     </row>
     <row r="52">
@@ -4785,7 +4785,7 @@
         <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>3877.5</v>
+        <v>3886.5</v>
       </c>
       <c r="I52" t="n">
         <v>518.7</v>
@@ -4794,7 +4794,7 @@
         <v>103.6</v>
       </c>
       <c r="K52" t="n">
-        <v>36756.8</v>
+        <v>36765.8</v>
       </c>
     </row>
     <row r="53">
@@ -4820,7 +4820,7 @@
         <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>3877.5</v>
+        <v>3886.5</v>
       </c>
       <c r="I53" t="n">
         <v>518.7</v>
@@ -4829,7 +4829,7 @@
         <v>103.6</v>
       </c>
       <c r="K53" t="n">
-        <v>36800.3</v>
+        <v>36809.3</v>
       </c>
     </row>
     <row r="54">
@@ -4855,7 +4855,7 @@
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>3877.5</v>
+        <v>3886.5</v>
       </c>
       <c r="I54" t="n">
         <v>518.7</v>
@@ -4864,7 +4864,7 @@
         <v>103.6</v>
       </c>
       <c r="K54" t="n">
-        <v>36841.3</v>
+        <v>36850.3</v>
       </c>
     </row>
     <row r="55">
@@ -4890,7 +4890,7 @@
         <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>3877.5</v>
+        <v>3886.5</v>
       </c>
       <c r="I55" t="n">
         <v>518.7</v>
@@ -4899,7 +4899,7 @@
         <v>103.6</v>
       </c>
       <c r="K55" t="n">
-        <v>37262.8</v>
+        <v>37271.8</v>
       </c>
     </row>
     <row r="56">
@@ -4925,7 +4925,7 @@
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>3886.5</v>
+        <v>3895.5</v>
       </c>
       <c r="I56" t="n">
         <v>518.7</v>
@@ -4934,7 +4934,7 @@
         <v>103.6</v>
       </c>
       <c r="K56" t="n">
-        <v>37739.2</v>
+        <v>37748.2</v>
       </c>
     </row>
     <row r="57">
@@ -4960,7 +4960,7 @@
         <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>3886.5</v>
+        <v>3895.5</v>
       </c>
       <c r="I57" t="n">
         <v>518.7</v>
@@ -4969,7 +4969,7 @@
         <v>103.6</v>
       </c>
       <c r="K57" t="n">
-        <v>37959.2</v>
+        <v>37968.2</v>
       </c>
     </row>
     <row r="58">
@@ -4995,7 +4995,7 @@
         <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>3886.5</v>
+        <v>3895.5</v>
       </c>
       <c r="I58" t="n">
         <v>664.1</v>
@@ -5004,7 +5004,7 @@
         <v>103.6</v>
       </c>
       <c r="K58" t="n">
-        <v>38379.1</v>
+        <v>38388.1</v>
       </c>
     </row>
     <row r="59">
@@ -5030,7 +5030,7 @@
         <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>3886.5</v>
+        <v>3895.5</v>
       </c>
       <c r="I59" t="n">
         <v>664.1</v>
@@ -5039,7 +5039,7 @@
         <v>103.6</v>
       </c>
       <c r="K59" t="n">
-        <v>38388.1</v>
+        <v>38397.1</v>
       </c>
     </row>
     <row r="60">
@@ -5065,7 +5065,7 @@
         <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>3886.5</v>
+        <v>3895.5</v>
       </c>
       <c r="I60" t="n">
         <v>664.1</v>
@@ -5074,7 +5074,7 @@
         <v>103.6</v>
       </c>
       <c r="K60" t="n">
-        <v>38402.2</v>
+        <v>38411.2</v>
       </c>
     </row>
     <row r="61">
@@ -5403,7 +5403,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F61"/>
+  <dimension ref="A1:K61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5414,27 +5414,52 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>CNE_rebuilt_coal_MW</t>
+          <t>Ember_year_end_used</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Ember_year_end_used</t>
+          <t>CNE_rebuilt_Coal_MW</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Ember_coal_MW</t>
+          <t>Coal_adjustment_MW</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Adjustment_MW</t>
+          <t>Coal_MW</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Coal_MW</t>
+          <t>CNE_rebuilt_Gas_MW</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Gas_adjustment_MW</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Gas_MW</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>CNE_rebuilt_Oil_MW</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Oil_adjustment_MW</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Oil_MW</t>
         </is>
       </c>
     </row>
@@ -5443,19 +5468,34 @@
         <v>44197</v>
       </c>
       <c r="B2" t="n">
+        <v>2020</v>
+      </c>
+      <c r="C2" t="n">
         <v>3533.5</v>
       </c>
-      <c r="C2" t="n">
-        <v>2020</v>
-      </c>
       <c r="D2" t="n">
-        <v>4940</v>
+        <v>5353.5</v>
       </c>
       <c r="E2" t="n">
-        <v>1820</v>
+        <v>8887</v>
       </c>
       <c r="F2" t="n">
-        <v>5353.5</v>
+        <v>4255.3</v>
+      </c>
+      <c r="G2" t="n">
+        <v>4255.3</v>
+      </c>
+      <c r="H2" t="n">
+        <v>8510.700000000001</v>
+      </c>
+      <c r="I2" t="n">
+        <v>3361.8</v>
+      </c>
+      <c r="J2" t="n">
+        <v>3516.5</v>
+      </c>
+      <c r="K2" t="n">
+        <v>6878.3</v>
       </c>
     </row>
     <row r="3">
@@ -5463,19 +5503,34 @@
         <v>44228</v>
       </c>
       <c r="B3" t="n">
+        <v>2020</v>
+      </c>
+      <c r="C3" t="n">
         <v>3533.5</v>
       </c>
-      <c r="C3" t="n">
-        <v>2020</v>
-      </c>
       <c r="D3" t="n">
-        <v>4940</v>
+        <v>5353.5</v>
       </c>
       <c r="E3" t="n">
-        <v>1820</v>
+        <v>8887</v>
       </c>
       <c r="F3" t="n">
-        <v>5353.5</v>
+        <v>4255.3</v>
+      </c>
+      <c r="G3" t="n">
+        <v>4255.3</v>
+      </c>
+      <c r="H3" t="n">
+        <v>8510.700000000001</v>
+      </c>
+      <c r="I3" t="n">
+        <v>3370.4</v>
+      </c>
+      <c r="J3" t="n">
+        <v>3516.5</v>
+      </c>
+      <c r="K3" t="n">
+        <v>6886.9</v>
       </c>
     </row>
     <row r="4">
@@ -5483,19 +5538,34 @@
         <v>44256</v>
       </c>
       <c r="B4" t="n">
+        <v>2020</v>
+      </c>
+      <c r="C4" t="n">
         <v>3533.5</v>
       </c>
-      <c r="C4" t="n">
-        <v>2020</v>
-      </c>
       <c r="D4" t="n">
-        <v>4940</v>
+        <v>5353.5</v>
       </c>
       <c r="E4" t="n">
-        <v>1820</v>
+        <v>8887</v>
       </c>
       <c r="F4" t="n">
-        <v>5353.5</v>
+        <v>4255.3</v>
+      </c>
+      <c r="G4" t="n">
+        <v>4255.3</v>
+      </c>
+      <c r="H4" t="n">
+        <v>8510.700000000001</v>
+      </c>
+      <c r="I4" t="n">
+        <v>3371.1</v>
+      </c>
+      <c r="J4" t="n">
+        <v>3516.5</v>
+      </c>
+      <c r="K4" t="n">
+        <v>6887.6</v>
       </c>
     </row>
     <row r="5">
@@ -5503,19 +5573,34 @@
         <v>44287</v>
       </c>
       <c r="B5" t="n">
+        <v>2020</v>
+      </c>
+      <c r="C5" t="n">
         <v>3533.5</v>
       </c>
-      <c r="C5" t="n">
-        <v>2020</v>
-      </c>
       <c r="D5" t="n">
-        <v>4940</v>
+        <v>5353.5</v>
       </c>
       <c r="E5" t="n">
-        <v>1820</v>
+        <v>8887</v>
       </c>
       <c r="F5" t="n">
-        <v>5353.5</v>
+        <v>4255.3</v>
+      </c>
+      <c r="G5" t="n">
+        <v>4255.3</v>
+      </c>
+      <c r="H5" t="n">
+        <v>8510.700000000001</v>
+      </c>
+      <c r="I5" t="n">
+        <v>3371.1</v>
+      </c>
+      <c r="J5" t="n">
+        <v>3516.5</v>
+      </c>
+      <c r="K5" t="n">
+        <v>6887.6</v>
       </c>
     </row>
     <row r="6">
@@ -5523,19 +5608,34 @@
         <v>44317</v>
       </c>
       <c r="B6" t="n">
+        <v>2020</v>
+      </c>
+      <c r="C6" t="n">
         <v>3533.5</v>
       </c>
-      <c r="C6" t="n">
-        <v>2020</v>
-      </c>
       <c r="D6" t="n">
-        <v>4940</v>
+        <v>5353.5</v>
       </c>
       <c r="E6" t="n">
-        <v>1820</v>
+        <v>8887</v>
       </c>
       <c r="F6" t="n">
-        <v>5353.5</v>
+        <v>4255.3</v>
+      </c>
+      <c r="G6" t="n">
+        <v>4255.3</v>
+      </c>
+      <c r="H6" t="n">
+        <v>8510.700000000001</v>
+      </c>
+      <c r="I6" t="n">
+        <v>3374</v>
+      </c>
+      <c r="J6" t="n">
+        <v>3516.5</v>
+      </c>
+      <c r="K6" t="n">
+        <v>6890.5</v>
       </c>
     </row>
     <row r="7">
@@ -5543,19 +5643,34 @@
         <v>44348</v>
       </c>
       <c r="B7" t="n">
+        <v>2020</v>
+      </c>
+      <c r="C7" t="n">
         <v>3533.5</v>
       </c>
-      <c r="C7" t="n">
-        <v>2020</v>
-      </c>
       <c r="D7" t="n">
-        <v>4940</v>
+        <v>5353.5</v>
       </c>
       <c r="E7" t="n">
-        <v>1820</v>
+        <v>8887</v>
       </c>
       <c r="F7" t="n">
-        <v>5353.5</v>
+        <v>4255.3</v>
+      </c>
+      <c r="G7" t="n">
+        <v>4255.3</v>
+      </c>
+      <c r="H7" t="n">
+        <v>8510.700000000001</v>
+      </c>
+      <c r="I7" t="n">
+        <v>3383</v>
+      </c>
+      <c r="J7" t="n">
+        <v>3516.5</v>
+      </c>
+      <c r="K7" t="n">
+        <v>6899.5</v>
       </c>
     </row>
     <row r="8">
@@ -5563,19 +5678,34 @@
         <v>44378</v>
       </c>
       <c r="B8" t="n">
+        <v>2020</v>
+      </c>
+      <c r="C8" t="n">
         <v>3533.5</v>
       </c>
-      <c r="C8" t="n">
-        <v>2020</v>
-      </c>
       <c r="D8" t="n">
-        <v>4940</v>
+        <v>5353.5</v>
       </c>
       <c r="E8" t="n">
-        <v>1820</v>
+        <v>8887</v>
       </c>
       <c r="F8" t="n">
-        <v>5353.5</v>
+        <v>4255.3</v>
+      </c>
+      <c r="G8" t="n">
+        <v>4255.3</v>
+      </c>
+      <c r="H8" t="n">
+        <v>8510.700000000001</v>
+      </c>
+      <c r="I8" t="n">
+        <v>3386</v>
+      </c>
+      <c r="J8" t="n">
+        <v>3516.5</v>
+      </c>
+      <c r="K8" t="n">
+        <v>6902.5</v>
       </c>
     </row>
     <row r="9">
@@ -5583,19 +5713,34 @@
         <v>44409</v>
       </c>
       <c r="B9" t="n">
+        <v>2020</v>
+      </c>
+      <c r="C9" t="n">
         <v>3533.5</v>
       </c>
-      <c r="C9" t="n">
-        <v>2020</v>
-      </c>
       <c r="D9" t="n">
-        <v>4940</v>
+        <v>5353.5</v>
       </c>
       <c r="E9" t="n">
-        <v>1820</v>
+        <v>8887</v>
       </c>
       <c r="F9" t="n">
-        <v>5353.5</v>
+        <v>4255.3</v>
+      </c>
+      <c r="G9" t="n">
+        <v>4255.3</v>
+      </c>
+      <c r="H9" t="n">
+        <v>8510.700000000001</v>
+      </c>
+      <c r="I9" t="n">
+        <v>3491.2</v>
+      </c>
+      <c r="J9" t="n">
+        <v>3516.5</v>
+      </c>
+      <c r="K9" t="n">
+        <v>7007.7</v>
       </c>
     </row>
     <row r="10">
@@ -5603,19 +5748,34 @@
         <v>44440</v>
       </c>
       <c r="B10" t="n">
+        <v>2020</v>
+      </c>
+      <c r="C10" t="n">
         <v>3533.5</v>
       </c>
-      <c r="C10" t="n">
-        <v>2020</v>
-      </c>
       <c r="D10" t="n">
-        <v>4940</v>
+        <v>5353.5</v>
       </c>
       <c r="E10" t="n">
-        <v>1820</v>
+        <v>8887</v>
       </c>
       <c r="F10" t="n">
-        <v>5353.5</v>
+        <v>4255.3</v>
+      </c>
+      <c r="G10" t="n">
+        <v>4255.3</v>
+      </c>
+      <c r="H10" t="n">
+        <v>8510.700000000001</v>
+      </c>
+      <c r="I10" t="n">
+        <v>3570</v>
+      </c>
+      <c r="J10" t="n">
+        <v>3516.5</v>
+      </c>
+      <c r="K10" t="n">
+        <v>7086.5</v>
       </c>
     </row>
     <row r="11">
@@ -5623,19 +5783,34 @@
         <v>44470</v>
       </c>
       <c r="B11" t="n">
+        <v>2020</v>
+      </c>
+      <c r="C11" t="n">
         <v>3533.5</v>
       </c>
-      <c r="C11" t="n">
-        <v>2020</v>
-      </c>
       <c r="D11" t="n">
-        <v>4940</v>
+        <v>5353.5</v>
       </c>
       <c r="E11" t="n">
-        <v>1820</v>
+        <v>8887</v>
       </c>
       <c r="F11" t="n">
-        <v>5353.5</v>
+        <v>4255.3</v>
+      </c>
+      <c r="G11" t="n">
+        <v>4255.3</v>
+      </c>
+      <c r="H11" t="n">
+        <v>8510.700000000001</v>
+      </c>
+      <c r="I11" t="n">
+        <v>3570</v>
+      </c>
+      <c r="J11" t="n">
+        <v>3516.5</v>
+      </c>
+      <c r="K11" t="n">
+        <v>7086.5</v>
       </c>
     </row>
     <row r="12">
@@ -5643,19 +5818,34 @@
         <v>44501</v>
       </c>
       <c r="B12" t="n">
+        <v>2020</v>
+      </c>
+      <c r="C12" t="n">
         <v>3533.5</v>
       </c>
-      <c r="C12" t="n">
-        <v>2020</v>
-      </c>
       <c r="D12" t="n">
-        <v>4940</v>
+        <v>5353.5</v>
       </c>
       <c r="E12" t="n">
-        <v>1820</v>
+        <v>8887</v>
       </c>
       <c r="F12" t="n">
-        <v>5353.5</v>
+        <v>4255.3</v>
+      </c>
+      <c r="G12" t="n">
+        <v>4255.3</v>
+      </c>
+      <c r="H12" t="n">
+        <v>8510.700000000001</v>
+      </c>
+      <c r="I12" t="n">
+        <v>3570</v>
+      </c>
+      <c r="J12" t="n">
+        <v>3516.5</v>
+      </c>
+      <c r="K12" t="n">
+        <v>7086.5</v>
       </c>
     </row>
     <row r="13">
@@ -5663,19 +5853,34 @@
         <v>44531</v>
       </c>
       <c r="B13" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C13" t="n">
         <v>3533.5</v>
       </c>
-      <c r="C13" t="n">
-        <v>2021</v>
-      </c>
       <c r="D13" t="n">
-        <v>4940</v>
+        <v>1820</v>
       </c>
       <c r="E13" t="n">
-        <v>1820</v>
+        <v>5353.5</v>
       </c>
       <c r="F13" t="n">
-        <v>5353.5</v>
+        <v>4255.3</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>4255.3</v>
+      </c>
+      <c r="I13" t="n">
+        <v>3570</v>
+      </c>
+      <c r="J13" t="n">
+        <v>296.4</v>
+      </c>
+      <c r="K13" t="n">
+        <v>3866.5</v>
       </c>
     </row>
     <row r="14">
@@ -5683,19 +5888,34 @@
         <v>44562</v>
       </c>
       <c r="B14" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C14" t="n">
         <v>3533.5</v>
       </c>
-      <c r="C14" t="n">
-        <v>2021</v>
-      </c>
       <c r="D14" t="n">
-        <v>4940</v>
+        <v>1820</v>
       </c>
       <c r="E14" t="n">
-        <v>1820</v>
+        <v>5353.5</v>
       </c>
       <c r="F14" t="n">
-        <v>5353.5</v>
+        <v>4255.3</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="n">
+        <v>4255.3</v>
+      </c>
+      <c r="I14" t="n">
+        <v>3753</v>
+      </c>
+      <c r="J14" t="n">
+        <v>296.4</v>
+      </c>
+      <c r="K14" t="n">
+        <v>4049.4</v>
       </c>
     </row>
     <row r="15">
@@ -5703,19 +5923,34 @@
         <v>44593</v>
       </c>
       <c r="B15" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C15" t="n">
         <v>3533.5</v>
       </c>
-      <c r="C15" t="n">
-        <v>2021</v>
-      </c>
       <c r="D15" t="n">
-        <v>4940</v>
+        <v>1820</v>
       </c>
       <c r="E15" t="n">
-        <v>1820</v>
+        <v>5353.5</v>
       </c>
       <c r="F15" t="n">
-        <v>5353.5</v>
+        <v>4255.3</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>4255.3</v>
+      </c>
+      <c r="I15" t="n">
+        <v>3756</v>
+      </c>
+      <c r="J15" t="n">
+        <v>296.4</v>
+      </c>
+      <c r="K15" t="n">
+        <v>4052.4</v>
       </c>
     </row>
     <row r="16">
@@ -5723,19 +5958,34 @@
         <v>44621</v>
       </c>
       <c r="B16" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C16" t="n">
         <v>3533.5</v>
       </c>
-      <c r="C16" t="n">
-        <v>2021</v>
-      </c>
       <c r="D16" t="n">
-        <v>4940</v>
+        <v>1820</v>
       </c>
       <c r="E16" t="n">
-        <v>1820</v>
+        <v>5353.5</v>
       </c>
       <c r="F16" t="n">
-        <v>5353.5</v>
+        <v>4255.3</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>4255.3</v>
+      </c>
+      <c r="I16" t="n">
+        <v>3756</v>
+      </c>
+      <c r="J16" t="n">
+        <v>296.4</v>
+      </c>
+      <c r="K16" t="n">
+        <v>4052.4</v>
       </c>
     </row>
     <row r="17">
@@ -5743,19 +5993,34 @@
         <v>44652</v>
       </c>
       <c r="B17" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C17" t="n">
         <v>3533.5</v>
       </c>
-      <c r="C17" t="n">
-        <v>2021</v>
-      </c>
       <c r="D17" t="n">
-        <v>4940</v>
+        <v>1820</v>
       </c>
       <c r="E17" t="n">
-        <v>1820</v>
+        <v>5353.5</v>
       </c>
       <c r="F17" t="n">
-        <v>5353.5</v>
+        <v>4255.3</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
+        <v>4255.3</v>
+      </c>
+      <c r="I17" t="n">
+        <v>3759</v>
+      </c>
+      <c r="J17" t="n">
+        <v>296.4</v>
+      </c>
+      <c r="K17" t="n">
+        <v>4055.4</v>
       </c>
     </row>
     <row r="18">
@@ -5763,19 +6028,34 @@
         <v>44682</v>
       </c>
       <c r="B18" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C18" t="n">
         <v>3533.5</v>
       </c>
-      <c r="C18" t="n">
-        <v>2021</v>
-      </c>
       <c r="D18" t="n">
-        <v>4940</v>
+        <v>1820</v>
       </c>
       <c r="E18" t="n">
-        <v>1820</v>
+        <v>5353.5</v>
       </c>
       <c r="F18" t="n">
-        <v>5353.5</v>
+        <v>4255.3</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
+        <v>4255.3</v>
+      </c>
+      <c r="I18" t="n">
+        <v>3761.5</v>
+      </c>
+      <c r="J18" t="n">
+        <v>296.4</v>
+      </c>
+      <c r="K18" t="n">
+        <v>4057.9</v>
       </c>
     </row>
     <row r="19">
@@ -5783,19 +6063,34 @@
         <v>44713</v>
       </c>
       <c r="B19" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C19" t="n">
         <v>3533.5</v>
       </c>
-      <c r="C19" t="n">
-        <v>2021</v>
-      </c>
       <c r="D19" t="n">
-        <v>4940</v>
+        <v>1820</v>
       </c>
       <c r="E19" t="n">
-        <v>1820</v>
+        <v>5353.5</v>
       </c>
       <c r="F19" t="n">
-        <v>5353.5</v>
+        <v>4255.3</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" t="n">
+        <v>4255.3</v>
+      </c>
+      <c r="I19" t="n">
+        <v>3761.5</v>
+      </c>
+      <c r="J19" t="n">
+        <v>296.4</v>
+      </c>
+      <c r="K19" t="n">
+        <v>4057.9</v>
       </c>
     </row>
     <row r="20">
@@ -5803,19 +6098,34 @@
         <v>44743</v>
       </c>
       <c r="B20" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C20" t="n">
         <v>3533.5</v>
       </c>
-      <c r="C20" t="n">
-        <v>2021</v>
-      </c>
       <c r="D20" t="n">
-        <v>4940</v>
+        <v>1820</v>
       </c>
       <c r="E20" t="n">
-        <v>1820</v>
+        <v>5353.5</v>
       </c>
       <c r="F20" t="n">
-        <v>5353.5</v>
+        <v>4255.3</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="n">
+        <v>4255.3</v>
+      </c>
+      <c r="I20" t="n">
+        <v>3761.5</v>
+      </c>
+      <c r="J20" t="n">
+        <v>296.4</v>
+      </c>
+      <c r="K20" t="n">
+        <v>4057.9</v>
       </c>
     </row>
     <row r="21">
@@ -5823,19 +6133,34 @@
         <v>44774</v>
       </c>
       <c r="B21" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C21" t="n">
         <v>3533.5</v>
       </c>
-      <c r="C21" t="n">
-        <v>2021</v>
-      </c>
       <c r="D21" t="n">
-        <v>4940</v>
+        <v>1820</v>
       </c>
       <c r="E21" t="n">
-        <v>1820</v>
+        <v>5353.5</v>
       </c>
       <c r="F21" t="n">
-        <v>5353.5</v>
+        <v>4255.3</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="n">
+        <v>4255.3</v>
+      </c>
+      <c r="I21" t="n">
+        <v>3761.5</v>
+      </c>
+      <c r="J21" t="n">
+        <v>296.4</v>
+      </c>
+      <c r="K21" t="n">
+        <v>4057.9</v>
       </c>
     </row>
     <row r="22">
@@ -5843,19 +6168,34 @@
         <v>44805</v>
       </c>
       <c r="B22" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C22" t="n">
         <v>3533.5</v>
       </c>
-      <c r="C22" t="n">
-        <v>2021</v>
-      </c>
       <c r="D22" t="n">
-        <v>4940</v>
+        <v>1820</v>
       </c>
       <c r="E22" t="n">
-        <v>1820</v>
+        <v>5353.5</v>
       </c>
       <c r="F22" t="n">
-        <v>5353.5</v>
+        <v>4255.3</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="n">
+        <v>4255.3</v>
+      </c>
+      <c r="I22" t="n">
+        <v>3761.5</v>
+      </c>
+      <c r="J22" t="n">
+        <v>296.4</v>
+      </c>
+      <c r="K22" t="n">
+        <v>4057.9</v>
       </c>
     </row>
     <row r="23">
@@ -5863,19 +6203,34 @@
         <v>44835</v>
       </c>
       <c r="B23" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C23" t="n">
         <v>3533.5</v>
       </c>
-      <c r="C23" t="n">
-        <v>2021</v>
-      </c>
       <c r="D23" t="n">
-        <v>4940</v>
+        <v>1820</v>
       </c>
       <c r="E23" t="n">
-        <v>1820</v>
+        <v>5353.5</v>
       </c>
       <c r="F23" t="n">
-        <v>5353.5</v>
+        <v>4255.3</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" t="n">
+        <v>4255.3</v>
+      </c>
+      <c r="I23" t="n">
+        <v>3764.5</v>
+      </c>
+      <c r="J23" t="n">
+        <v>296.4</v>
+      </c>
+      <c r="K23" t="n">
+        <v>4060.9</v>
       </c>
     </row>
     <row r="24">
@@ -5883,19 +6238,34 @@
         <v>44866</v>
       </c>
       <c r="B24" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C24" t="n">
         <v>3533.5</v>
       </c>
-      <c r="C24" t="n">
-        <v>2021</v>
-      </c>
       <c r="D24" t="n">
-        <v>4940</v>
+        <v>1820</v>
       </c>
       <c r="E24" t="n">
-        <v>1820</v>
+        <v>5353.5</v>
       </c>
       <c r="F24" t="n">
-        <v>5353.5</v>
+        <v>4255.3</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="n">
+        <v>4255.3</v>
+      </c>
+      <c r="I24" t="n">
+        <v>3789.9</v>
+      </c>
+      <c r="J24" t="n">
+        <v>296.4</v>
+      </c>
+      <c r="K24" t="n">
+        <v>4086.3</v>
       </c>
     </row>
     <row r="25">
@@ -5903,19 +6273,34 @@
         <v>44896</v>
       </c>
       <c r="B25" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C25" t="n">
         <v>3533.5</v>
       </c>
-      <c r="C25" t="n">
-        <v>2022</v>
-      </c>
       <c r="D25" t="n">
-        <v>4320</v>
+        <v>1200</v>
       </c>
       <c r="E25" t="n">
-        <v>1200</v>
+        <v>4733.5</v>
       </c>
       <c r="F25" t="n">
-        <v>4733.5</v>
+        <v>4255.3</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="n">
+        <v>4255.3</v>
+      </c>
+      <c r="I25" t="n">
+        <v>3789.9</v>
+      </c>
+      <c r="J25" t="n">
+        <v>76.59999999999999</v>
+      </c>
+      <c r="K25" t="n">
+        <v>3866.5</v>
       </c>
     </row>
     <row r="26">
@@ -5923,19 +6308,34 @@
         <v>44927</v>
       </c>
       <c r="B26" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C26" t="n">
         <v>3533.5</v>
       </c>
-      <c r="C26" t="n">
-        <v>2022</v>
-      </c>
       <c r="D26" t="n">
-        <v>4320</v>
+        <v>1200</v>
       </c>
       <c r="E26" t="n">
-        <v>1200</v>
+        <v>4733.5</v>
       </c>
       <c r="F26" t="n">
-        <v>4733.5</v>
+        <v>4255.3</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" t="n">
+        <v>4255.3</v>
+      </c>
+      <c r="I26" t="n">
+        <v>3791.2</v>
+      </c>
+      <c r="J26" t="n">
+        <v>76.59999999999999</v>
+      </c>
+      <c r="K26" t="n">
+        <v>3867.8</v>
       </c>
     </row>
     <row r="27">
@@ -5943,19 +6343,34 @@
         <v>44958</v>
       </c>
       <c r="B27" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C27" t="n">
         <v>3533.5</v>
       </c>
-      <c r="C27" t="n">
-        <v>2022</v>
-      </c>
       <c r="D27" t="n">
-        <v>4320</v>
+        <v>1200</v>
       </c>
       <c r="E27" t="n">
-        <v>1200</v>
+        <v>4733.5</v>
       </c>
       <c r="F27" t="n">
-        <v>4733.5</v>
+        <v>4255.3</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" t="n">
+        <v>4255.3</v>
+      </c>
+      <c r="I27" t="n">
+        <v>3794.2</v>
+      </c>
+      <c r="J27" t="n">
+        <v>76.59999999999999</v>
+      </c>
+      <c r="K27" t="n">
+        <v>3870.8</v>
       </c>
     </row>
     <row r="28">
@@ -5963,19 +6378,34 @@
         <v>44986</v>
       </c>
       <c r="B28" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C28" t="n">
         <v>3533.5</v>
       </c>
-      <c r="C28" t="n">
-        <v>2022</v>
-      </c>
       <c r="D28" t="n">
-        <v>4320</v>
+        <v>1200</v>
       </c>
       <c r="E28" t="n">
-        <v>1200</v>
+        <v>4733.5</v>
       </c>
       <c r="F28" t="n">
-        <v>4733.5</v>
+        <v>4255.3</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" t="n">
+        <v>4255.3</v>
+      </c>
+      <c r="I28" t="n">
+        <v>3797.2</v>
+      </c>
+      <c r="J28" t="n">
+        <v>76.59999999999999</v>
+      </c>
+      <c r="K28" t="n">
+        <v>3873.8</v>
       </c>
     </row>
     <row r="29">
@@ -5983,19 +6413,34 @@
         <v>45017</v>
       </c>
       <c r="B29" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C29" t="n">
         <v>3533.5</v>
       </c>
-      <c r="C29" t="n">
-        <v>2022</v>
-      </c>
       <c r="D29" t="n">
-        <v>4320</v>
+        <v>1200</v>
       </c>
       <c r="E29" t="n">
-        <v>1200</v>
+        <v>4733.5</v>
       </c>
       <c r="F29" t="n">
-        <v>4733.5</v>
+        <v>4255.3</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" t="n">
+        <v>4255.3</v>
+      </c>
+      <c r="I29" t="n">
+        <v>3797.2</v>
+      </c>
+      <c r="J29" t="n">
+        <v>76.59999999999999</v>
+      </c>
+      <c r="K29" t="n">
+        <v>3873.8</v>
       </c>
     </row>
     <row r="30">
@@ -6003,19 +6448,34 @@
         <v>45047</v>
       </c>
       <c r="B30" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C30" t="n">
         <v>3533.5</v>
       </c>
-      <c r="C30" t="n">
-        <v>2022</v>
-      </c>
       <c r="D30" t="n">
-        <v>4320</v>
+        <v>1200</v>
       </c>
       <c r="E30" t="n">
-        <v>1200</v>
+        <v>4733.5</v>
       </c>
       <c r="F30" t="n">
-        <v>4733.5</v>
+        <v>4255.3</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" t="n">
+        <v>4255.3</v>
+      </c>
+      <c r="I30" t="n">
+        <v>3797.2</v>
+      </c>
+      <c r="J30" t="n">
+        <v>76.59999999999999</v>
+      </c>
+      <c r="K30" t="n">
+        <v>3873.8</v>
       </c>
     </row>
     <row r="31">
@@ -6023,19 +6483,34 @@
         <v>45078</v>
       </c>
       <c r="B31" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C31" t="n">
         <v>3533.5</v>
       </c>
-      <c r="C31" t="n">
-        <v>2022</v>
-      </c>
       <c r="D31" t="n">
-        <v>4320</v>
+        <v>1200</v>
       </c>
       <c r="E31" t="n">
-        <v>1200</v>
+        <v>4733.5</v>
       </c>
       <c r="F31" t="n">
-        <v>4733.5</v>
+        <v>4255.3</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" t="n">
+        <v>4255.3</v>
+      </c>
+      <c r="I31" t="n">
+        <v>3803.2</v>
+      </c>
+      <c r="J31" t="n">
+        <v>76.59999999999999</v>
+      </c>
+      <c r="K31" t="n">
+        <v>3879.8</v>
       </c>
     </row>
     <row r="32">
@@ -6043,19 +6518,34 @@
         <v>45108</v>
       </c>
       <c r="B32" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C32" t="n">
         <v>3533.5</v>
       </c>
-      <c r="C32" t="n">
-        <v>2022</v>
-      </c>
       <c r="D32" t="n">
-        <v>4320</v>
+        <v>1200</v>
       </c>
       <c r="E32" t="n">
-        <v>1200</v>
+        <v>4733.5</v>
       </c>
       <c r="F32" t="n">
-        <v>4733.5</v>
+        <v>4255.3</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" t="n">
+        <v>4255.3</v>
+      </c>
+      <c r="I32" t="n">
+        <v>3803.2</v>
+      </c>
+      <c r="J32" t="n">
+        <v>76.59999999999999</v>
+      </c>
+      <c r="K32" t="n">
+        <v>3879.8</v>
       </c>
     </row>
     <row r="33">
@@ -6063,19 +6553,34 @@
         <v>45139</v>
       </c>
       <c r="B33" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C33" t="n">
         <v>3533.5</v>
       </c>
-      <c r="C33" t="n">
-        <v>2022</v>
-      </c>
       <c r="D33" t="n">
-        <v>4320</v>
+        <v>1200</v>
       </c>
       <c r="E33" t="n">
-        <v>1200</v>
+        <v>4733.5</v>
       </c>
       <c r="F33" t="n">
-        <v>4733.5</v>
+        <v>4255.3</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" t="n">
+        <v>4255.3</v>
+      </c>
+      <c r="I33" t="n">
+        <v>3803.2</v>
+      </c>
+      <c r="J33" t="n">
+        <v>76.59999999999999</v>
+      </c>
+      <c r="K33" t="n">
+        <v>3879.8</v>
       </c>
     </row>
     <row r="34">
@@ -6083,19 +6588,34 @@
         <v>45170</v>
       </c>
       <c r="B34" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C34" t="n">
         <v>3533.5</v>
       </c>
-      <c r="C34" t="n">
-        <v>2022</v>
-      </c>
       <c r="D34" t="n">
-        <v>4320</v>
+        <v>1200</v>
       </c>
       <c r="E34" t="n">
-        <v>1200</v>
+        <v>4733.5</v>
       </c>
       <c r="F34" t="n">
-        <v>4733.5</v>
+        <v>4255.3</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" t="n">
+        <v>4255.3</v>
+      </c>
+      <c r="I34" t="n">
+        <v>3806.2</v>
+      </c>
+      <c r="J34" t="n">
+        <v>76.59999999999999</v>
+      </c>
+      <c r="K34" t="n">
+        <v>3882.8</v>
       </c>
     </row>
     <row r="35">
@@ -6103,19 +6623,34 @@
         <v>45200</v>
       </c>
       <c r="B35" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C35" t="n">
         <v>3533.5</v>
       </c>
-      <c r="C35" t="n">
-        <v>2022</v>
-      </c>
       <c r="D35" t="n">
-        <v>4320</v>
+        <v>1200</v>
       </c>
       <c r="E35" t="n">
-        <v>1200</v>
+        <v>4733.5</v>
       </c>
       <c r="F35" t="n">
-        <v>4733.5</v>
+        <v>4255.3</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" t="n">
+        <v>4255.3</v>
+      </c>
+      <c r="I35" t="n">
+        <v>3809.2</v>
+      </c>
+      <c r="J35" t="n">
+        <v>76.59999999999999</v>
+      </c>
+      <c r="K35" t="n">
+        <v>3885.8</v>
       </c>
     </row>
     <row r="36">
@@ -6123,19 +6658,34 @@
         <v>45231</v>
       </c>
       <c r="B36" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C36" t="n">
         <v>3533.5</v>
       </c>
-      <c r="C36" t="n">
-        <v>2022</v>
-      </c>
       <c r="D36" t="n">
-        <v>4320</v>
+        <v>1200</v>
       </c>
       <c r="E36" t="n">
-        <v>1200</v>
+        <v>4733.5</v>
       </c>
       <c r="F36" t="n">
-        <v>4733.5</v>
+        <v>4255.3</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" t="n">
+        <v>4255.3</v>
+      </c>
+      <c r="I36" t="n">
+        <v>3877</v>
+      </c>
+      <c r="J36" t="n">
+        <v>76.59999999999999</v>
+      </c>
+      <c r="K36" t="n">
+        <v>3953.6</v>
       </c>
     </row>
     <row r="37">
@@ -6143,19 +6693,34 @@
         <v>45261</v>
       </c>
       <c r="B37" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C37" t="n">
         <v>3533.5</v>
       </c>
-      <c r="C37" t="n">
-        <v>2023</v>
-      </c>
       <c r="D37" t="n">
-        <v>4100</v>
+        <v>980</v>
       </c>
       <c r="E37" t="n">
-        <v>980</v>
+        <v>4513.5</v>
       </c>
       <c r="F37" t="n">
-        <v>4513.5</v>
+        <v>4255.3</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" t="n">
+        <v>4255.3</v>
+      </c>
+      <c r="I37" t="n">
+        <v>3877</v>
+      </c>
+      <c r="J37" t="n">
+        <v>-60.5</v>
+      </c>
+      <c r="K37" t="n">
+        <v>3816.5</v>
       </c>
     </row>
     <row r="38">
@@ -6163,19 +6728,34 @@
         <v>45292</v>
       </c>
       <c r="B38" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C38" t="n">
         <v>3533.5</v>
       </c>
-      <c r="C38" t="n">
-        <v>2023</v>
-      </c>
       <c r="D38" t="n">
-        <v>4100</v>
+        <v>980</v>
       </c>
       <c r="E38" t="n">
-        <v>980</v>
+        <v>4513.5</v>
       </c>
       <c r="F38" t="n">
-        <v>4513.5</v>
+        <v>4255.3</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" t="n">
+        <v>4255.3</v>
+      </c>
+      <c r="I38" t="n">
+        <v>3877</v>
+      </c>
+      <c r="J38" t="n">
+        <v>-60.5</v>
+      </c>
+      <c r="K38" t="n">
+        <v>3816.5</v>
       </c>
     </row>
     <row r="39">
@@ -6183,19 +6763,34 @@
         <v>45323</v>
       </c>
       <c r="B39" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C39" t="n">
         <v>3533.5</v>
       </c>
-      <c r="C39" t="n">
-        <v>2023</v>
-      </c>
       <c r="D39" t="n">
-        <v>4100</v>
+        <v>980</v>
       </c>
       <c r="E39" t="n">
-        <v>980</v>
+        <v>4513.5</v>
       </c>
       <c r="F39" t="n">
-        <v>4513.5</v>
+        <v>4255.3</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" t="n">
+        <v>4255.3</v>
+      </c>
+      <c r="I39" t="n">
+        <v>3877</v>
+      </c>
+      <c r="J39" t="n">
+        <v>-60.5</v>
+      </c>
+      <c r="K39" t="n">
+        <v>3816.5</v>
       </c>
     </row>
     <row r="40">
@@ -6203,19 +6798,34 @@
         <v>45352</v>
       </c>
       <c r="B40" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C40" t="n">
         <v>3533.5</v>
       </c>
-      <c r="C40" t="n">
-        <v>2023</v>
-      </c>
       <c r="D40" t="n">
-        <v>4100</v>
+        <v>980</v>
       </c>
       <c r="E40" t="n">
-        <v>980</v>
+        <v>4513.5</v>
       </c>
       <c r="F40" t="n">
-        <v>4513.5</v>
+        <v>4255.3</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" t="n">
+        <v>4255.3</v>
+      </c>
+      <c r="I40" t="n">
+        <v>3877</v>
+      </c>
+      <c r="J40" t="n">
+        <v>-60.5</v>
+      </c>
+      <c r="K40" t="n">
+        <v>3816.5</v>
       </c>
     </row>
     <row r="41">
@@ -6223,19 +6833,34 @@
         <v>45383</v>
       </c>
       <c r="B41" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C41" t="n">
         <v>3533.5</v>
       </c>
-      <c r="C41" t="n">
-        <v>2023</v>
-      </c>
       <c r="D41" t="n">
-        <v>4100</v>
+        <v>980</v>
       </c>
       <c r="E41" t="n">
-        <v>980</v>
+        <v>4513.5</v>
       </c>
       <c r="F41" t="n">
-        <v>4513.5</v>
+        <v>4255.3</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" t="n">
+        <v>4255.3</v>
+      </c>
+      <c r="I41" t="n">
+        <v>3877</v>
+      </c>
+      <c r="J41" t="n">
+        <v>-60.5</v>
+      </c>
+      <c r="K41" t="n">
+        <v>3816.5</v>
       </c>
     </row>
     <row r="42">
@@ -6243,19 +6868,34 @@
         <v>45413</v>
       </c>
       <c r="B42" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C42" t="n">
         <v>3533.5</v>
       </c>
-      <c r="C42" t="n">
-        <v>2023</v>
-      </c>
       <c r="D42" t="n">
-        <v>4100</v>
+        <v>980</v>
       </c>
       <c r="E42" t="n">
-        <v>980</v>
+        <v>4513.5</v>
       </c>
       <c r="F42" t="n">
-        <v>4513.5</v>
+        <v>4255.3</v>
+      </c>
+      <c r="G42" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" t="n">
+        <v>4255.3</v>
+      </c>
+      <c r="I42" t="n">
+        <v>3877</v>
+      </c>
+      <c r="J42" t="n">
+        <v>-60.5</v>
+      </c>
+      <c r="K42" t="n">
+        <v>3816.5</v>
       </c>
     </row>
     <row r="43">
@@ -6263,19 +6903,34 @@
         <v>45444</v>
       </c>
       <c r="B43" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C43" t="n">
         <v>3533.5</v>
       </c>
-      <c r="C43" t="n">
-        <v>2023</v>
-      </c>
       <c r="D43" t="n">
-        <v>4100</v>
+        <v>980</v>
       </c>
       <c r="E43" t="n">
-        <v>980</v>
+        <v>4513.5</v>
       </c>
       <c r="F43" t="n">
-        <v>4513.5</v>
+        <v>4255.3</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" t="n">
+        <v>4255.3</v>
+      </c>
+      <c r="I43" t="n">
+        <v>3877.5</v>
+      </c>
+      <c r="J43" t="n">
+        <v>-60.5</v>
+      </c>
+      <c r="K43" t="n">
+        <v>3817</v>
       </c>
     </row>
     <row r="44">
@@ -6283,19 +6938,34 @@
         <v>45474</v>
       </c>
       <c r="B44" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C44" t="n">
         <v>3533.5</v>
       </c>
-      <c r="C44" t="n">
-        <v>2023</v>
-      </c>
       <c r="D44" t="n">
-        <v>4100</v>
+        <v>980</v>
       </c>
       <c r="E44" t="n">
-        <v>980</v>
+        <v>4513.5</v>
       </c>
       <c r="F44" t="n">
-        <v>4513.5</v>
+        <v>4255.3</v>
+      </c>
+      <c r="G44" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" t="n">
+        <v>4255.3</v>
+      </c>
+      <c r="I44" t="n">
+        <v>3877.5</v>
+      </c>
+      <c r="J44" t="n">
+        <v>-60.5</v>
+      </c>
+      <c r="K44" t="n">
+        <v>3817</v>
       </c>
     </row>
     <row r="45">
@@ -6303,19 +6973,34 @@
         <v>45505</v>
       </c>
       <c r="B45" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C45" t="n">
         <v>3533.5</v>
       </c>
-      <c r="C45" t="n">
-        <v>2023</v>
-      </c>
       <c r="D45" t="n">
-        <v>4100</v>
+        <v>980</v>
       </c>
       <c r="E45" t="n">
-        <v>980</v>
+        <v>4513.5</v>
       </c>
       <c r="F45" t="n">
-        <v>4513.5</v>
+        <v>4255.3</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" t="n">
+        <v>4255.3</v>
+      </c>
+      <c r="I45" t="n">
+        <v>3877.5</v>
+      </c>
+      <c r="J45" t="n">
+        <v>-60.5</v>
+      </c>
+      <c r="K45" t="n">
+        <v>3817</v>
       </c>
     </row>
     <row r="46">
@@ -6323,19 +7008,34 @@
         <v>45536</v>
       </c>
       <c r="B46" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C46" t="n">
         <v>3533.5</v>
       </c>
-      <c r="C46" t="n">
-        <v>2023</v>
-      </c>
       <c r="D46" t="n">
-        <v>4100</v>
+        <v>980</v>
       </c>
       <c r="E46" t="n">
-        <v>980</v>
+        <v>4513.5</v>
       </c>
       <c r="F46" t="n">
-        <v>4513.5</v>
+        <v>4255.3</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" t="n">
+        <v>4255.3</v>
+      </c>
+      <c r="I46" t="n">
+        <v>3877.5</v>
+      </c>
+      <c r="J46" t="n">
+        <v>-60.5</v>
+      </c>
+      <c r="K46" t="n">
+        <v>3817</v>
       </c>
     </row>
     <row r="47">
@@ -6343,19 +7043,34 @@
         <v>45566</v>
       </c>
       <c r="B47" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C47" t="n">
         <v>3533.5</v>
       </c>
-      <c r="C47" t="n">
-        <v>2023</v>
-      </c>
       <c r="D47" t="n">
-        <v>4100</v>
+        <v>980</v>
       </c>
       <c r="E47" t="n">
-        <v>980</v>
+        <v>4513.5</v>
       </c>
       <c r="F47" t="n">
-        <v>4513.5</v>
+        <v>4255.3</v>
+      </c>
+      <c r="G47" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" t="n">
+        <v>4255.3</v>
+      </c>
+      <c r="I47" t="n">
+        <v>3877.5</v>
+      </c>
+      <c r="J47" t="n">
+        <v>-60.5</v>
+      </c>
+      <c r="K47" t="n">
+        <v>3817</v>
       </c>
     </row>
     <row r="48">
@@ -6363,19 +7078,34 @@
         <v>45597</v>
       </c>
       <c r="B48" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C48" t="n">
         <v>3533.5</v>
       </c>
-      <c r="C48" t="n">
-        <v>2023</v>
-      </c>
       <c r="D48" t="n">
-        <v>4100</v>
+        <v>980</v>
       </c>
       <c r="E48" t="n">
-        <v>980</v>
+        <v>4513.5</v>
       </c>
       <c r="F48" t="n">
-        <v>4513.5</v>
+        <v>4255.3</v>
+      </c>
+      <c r="G48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" t="n">
+        <v>4255.3</v>
+      </c>
+      <c r="I48" t="n">
+        <v>3877.5</v>
+      </c>
+      <c r="J48" t="n">
+        <v>-60.5</v>
+      </c>
+      <c r="K48" t="n">
+        <v>3817</v>
       </c>
     </row>
     <row r="49">
@@ -6383,19 +7113,34 @@
         <v>45627</v>
       </c>
       <c r="B49" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C49" t="n">
         <v>3533.5</v>
       </c>
-      <c r="C49" t="n">
-        <v>2024</v>
-      </c>
       <c r="D49" t="n">
-        <v>3830</v>
+        <v>710</v>
       </c>
       <c r="E49" t="n">
-        <v>710</v>
+        <v>4243.5</v>
       </c>
       <c r="F49" t="n">
-        <v>4243.5</v>
+        <v>4255.3</v>
+      </c>
+      <c r="G49" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" t="n">
+        <v>4255.3</v>
+      </c>
+      <c r="I49" t="n">
+        <v>3877.5</v>
+      </c>
+      <c r="J49" t="n">
+        <v>9</v>
+      </c>
+      <c r="K49" t="n">
+        <v>3886.5</v>
       </c>
     </row>
     <row r="50">
@@ -6403,19 +7148,34 @@
         <v>45658</v>
       </c>
       <c r="B50" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C50" t="n">
         <v>3533.5</v>
       </c>
-      <c r="C50" t="n">
-        <v>2024</v>
-      </c>
       <c r="D50" t="n">
-        <v>3830</v>
+        <v>710</v>
       </c>
       <c r="E50" t="n">
-        <v>710</v>
+        <v>4243.5</v>
       </c>
       <c r="F50" t="n">
-        <v>4243.5</v>
+        <v>4255.3</v>
+      </c>
+      <c r="G50" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" t="n">
+        <v>4255.3</v>
+      </c>
+      <c r="I50" t="n">
+        <v>3877.5</v>
+      </c>
+      <c r="J50" t="n">
+        <v>9</v>
+      </c>
+      <c r="K50" t="n">
+        <v>3886.5</v>
       </c>
     </row>
     <row r="51">
@@ -6423,19 +7183,34 @@
         <v>45689</v>
       </c>
       <c r="B51" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C51" t="n">
         <v>3533.5</v>
       </c>
-      <c r="C51" t="n">
-        <v>2024</v>
-      </c>
       <c r="D51" t="n">
-        <v>3830</v>
+        <v>710</v>
       </c>
       <c r="E51" t="n">
-        <v>710</v>
+        <v>4243.5</v>
       </c>
       <c r="F51" t="n">
-        <v>4243.5</v>
+        <v>4255.3</v>
+      </c>
+      <c r="G51" t="n">
+        <v>0</v>
+      </c>
+      <c r="H51" t="n">
+        <v>4255.3</v>
+      </c>
+      <c r="I51" t="n">
+        <v>3877.5</v>
+      </c>
+      <c r="J51" t="n">
+        <v>9</v>
+      </c>
+      <c r="K51" t="n">
+        <v>3886.5</v>
       </c>
     </row>
     <row r="52">
@@ -6443,19 +7218,34 @@
         <v>45717</v>
       </c>
       <c r="B52" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C52" t="n">
         <v>3533.5</v>
       </c>
-      <c r="C52" t="n">
-        <v>2024</v>
-      </c>
       <c r="D52" t="n">
-        <v>3830</v>
+        <v>710</v>
       </c>
       <c r="E52" t="n">
-        <v>710</v>
+        <v>4243.5</v>
       </c>
       <c r="F52" t="n">
-        <v>4243.5</v>
+        <v>4255.3</v>
+      </c>
+      <c r="G52" t="n">
+        <v>0</v>
+      </c>
+      <c r="H52" t="n">
+        <v>4255.3</v>
+      </c>
+      <c r="I52" t="n">
+        <v>3877.5</v>
+      </c>
+      <c r="J52" t="n">
+        <v>9</v>
+      </c>
+      <c r="K52" t="n">
+        <v>3886.5</v>
       </c>
     </row>
     <row r="53">
@@ -6463,19 +7253,34 @@
         <v>45748</v>
       </c>
       <c r="B53" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C53" t="n">
         <v>3533.5</v>
       </c>
-      <c r="C53" t="n">
-        <v>2024</v>
-      </c>
       <c r="D53" t="n">
-        <v>3830</v>
+        <v>710</v>
       </c>
       <c r="E53" t="n">
-        <v>710</v>
+        <v>4243.5</v>
       </c>
       <c r="F53" t="n">
-        <v>4243.5</v>
+        <v>4255.3</v>
+      </c>
+      <c r="G53" t="n">
+        <v>0</v>
+      </c>
+      <c r="H53" t="n">
+        <v>4255.3</v>
+      </c>
+      <c r="I53" t="n">
+        <v>3877.5</v>
+      </c>
+      <c r="J53" t="n">
+        <v>9</v>
+      </c>
+      <c r="K53" t="n">
+        <v>3886.5</v>
       </c>
     </row>
     <row r="54">
@@ -6483,19 +7288,34 @@
         <v>45778</v>
       </c>
       <c r="B54" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C54" t="n">
         <v>3533.5</v>
       </c>
-      <c r="C54" t="n">
-        <v>2024</v>
-      </c>
       <c r="D54" t="n">
-        <v>3830</v>
+        <v>710</v>
       </c>
       <c r="E54" t="n">
-        <v>710</v>
+        <v>4243.5</v>
       </c>
       <c r="F54" t="n">
-        <v>4243.5</v>
+        <v>4255.3</v>
+      </c>
+      <c r="G54" t="n">
+        <v>0</v>
+      </c>
+      <c r="H54" t="n">
+        <v>4255.3</v>
+      </c>
+      <c r="I54" t="n">
+        <v>3877.5</v>
+      </c>
+      <c r="J54" t="n">
+        <v>9</v>
+      </c>
+      <c r="K54" t="n">
+        <v>3886.5</v>
       </c>
     </row>
     <row r="55">
@@ -6503,19 +7323,34 @@
         <v>45809</v>
       </c>
       <c r="B55" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C55" t="n">
         <v>3533.5</v>
       </c>
-      <c r="C55" t="n">
-        <v>2024</v>
-      </c>
       <c r="D55" t="n">
-        <v>3830</v>
+        <v>710</v>
       </c>
       <c r="E55" t="n">
-        <v>710</v>
+        <v>4243.5</v>
       </c>
       <c r="F55" t="n">
-        <v>4243.5</v>
+        <v>4255.3</v>
+      </c>
+      <c r="G55" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" t="n">
+        <v>4255.3</v>
+      </c>
+      <c r="I55" t="n">
+        <v>3877.5</v>
+      </c>
+      <c r="J55" t="n">
+        <v>9</v>
+      </c>
+      <c r="K55" t="n">
+        <v>3886.5</v>
       </c>
     </row>
     <row r="56">
@@ -6523,19 +7358,34 @@
         <v>45839</v>
       </c>
       <c r="B56" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C56" t="n">
         <v>3533.5</v>
       </c>
-      <c r="C56" t="n">
-        <v>2024</v>
-      </c>
       <c r="D56" t="n">
-        <v>3830</v>
+        <v>710</v>
       </c>
       <c r="E56" t="n">
-        <v>710</v>
+        <v>4243.5</v>
       </c>
       <c r="F56" t="n">
-        <v>4243.5</v>
+        <v>4255.3</v>
+      </c>
+      <c r="G56" t="n">
+        <v>0</v>
+      </c>
+      <c r="H56" t="n">
+        <v>4255.3</v>
+      </c>
+      <c r="I56" t="n">
+        <v>3886.5</v>
+      </c>
+      <c r="J56" t="n">
+        <v>9</v>
+      </c>
+      <c r="K56" t="n">
+        <v>3895.5</v>
       </c>
     </row>
     <row r="57">
@@ -6543,19 +7393,34 @@
         <v>45870</v>
       </c>
       <c r="B57" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C57" t="n">
         <v>3533.5</v>
       </c>
-      <c r="C57" t="n">
-        <v>2024</v>
-      </c>
       <c r="D57" t="n">
-        <v>3830</v>
+        <v>710</v>
       </c>
       <c r="E57" t="n">
-        <v>710</v>
+        <v>4243.5</v>
       </c>
       <c r="F57" t="n">
-        <v>4243.5</v>
+        <v>4255.3</v>
+      </c>
+      <c r="G57" t="n">
+        <v>0</v>
+      </c>
+      <c r="H57" t="n">
+        <v>4255.3</v>
+      </c>
+      <c r="I57" t="n">
+        <v>3886.5</v>
+      </c>
+      <c r="J57" t="n">
+        <v>9</v>
+      </c>
+      <c r="K57" t="n">
+        <v>3895.5</v>
       </c>
     </row>
     <row r="58">
@@ -6563,19 +7428,34 @@
         <v>45901</v>
       </c>
       <c r="B58" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C58" t="n">
         <v>3533.5</v>
       </c>
-      <c r="C58" t="n">
-        <v>2024</v>
-      </c>
       <c r="D58" t="n">
-        <v>3830</v>
+        <v>710</v>
       </c>
       <c r="E58" t="n">
-        <v>710</v>
+        <v>4243.5</v>
       </c>
       <c r="F58" t="n">
-        <v>4243.5</v>
+        <v>4255.3</v>
+      </c>
+      <c r="G58" t="n">
+        <v>0</v>
+      </c>
+      <c r="H58" t="n">
+        <v>4255.3</v>
+      </c>
+      <c r="I58" t="n">
+        <v>3886.5</v>
+      </c>
+      <c r="J58" t="n">
+        <v>9</v>
+      </c>
+      <c r="K58" t="n">
+        <v>3895.5</v>
       </c>
     </row>
     <row r="59">
@@ -6583,19 +7463,34 @@
         <v>45931</v>
       </c>
       <c r="B59" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C59" t="n">
         <v>3533.5</v>
       </c>
-      <c r="C59" t="n">
-        <v>2024</v>
-      </c>
       <c r="D59" t="n">
-        <v>3830</v>
+        <v>710</v>
       </c>
       <c r="E59" t="n">
-        <v>710</v>
+        <v>4243.5</v>
       </c>
       <c r="F59" t="n">
-        <v>4243.5</v>
+        <v>4255.3</v>
+      </c>
+      <c r="G59" t="n">
+        <v>0</v>
+      </c>
+      <c r="H59" t="n">
+        <v>4255.3</v>
+      </c>
+      <c r="I59" t="n">
+        <v>3886.5</v>
+      </c>
+      <c r="J59" t="n">
+        <v>9</v>
+      </c>
+      <c r="K59" t="n">
+        <v>3895.5</v>
       </c>
     </row>
     <row r="60">
@@ -6603,19 +7498,34 @@
         <v>45962</v>
       </c>
       <c r="B60" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C60" t="n">
         <v>3533.5</v>
       </c>
-      <c r="C60" t="n">
-        <v>2024</v>
-      </c>
       <c r="D60" t="n">
-        <v>3830</v>
+        <v>710</v>
       </c>
       <c r="E60" t="n">
-        <v>710</v>
+        <v>4243.5</v>
       </c>
       <c r="F60" t="n">
-        <v>4243.5</v>
+        <v>4255.3</v>
+      </c>
+      <c r="G60" t="n">
+        <v>0</v>
+      </c>
+      <c r="H60" t="n">
+        <v>4255.3</v>
+      </c>
+      <c r="I60" t="n">
+        <v>3886.5</v>
+      </c>
+      <c r="J60" t="n">
+        <v>9</v>
+      </c>
+      <c r="K60" t="n">
+        <v>3895.5</v>
       </c>
     </row>
     <row r="61">
@@ -6623,19 +7533,34 @@
         <v>45992</v>
       </c>
       <c r="B61" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C61" t="n">
         <v>3533.5</v>
       </c>
-      <c r="C61" t="n">
-        <v>2025</v>
-      </c>
       <c r="D61" t="n">
-        <v>3120</v>
+        <v>0</v>
       </c>
       <c r="E61" t="n">
+        <v>3533.5</v>
+      </c>
+      <c r="F61" t="n">
+        <v>4255.3</v>
+      </c>
+      <c r="G61" t="n">
         <v>0</v>
       </c>
-      <c r="F61" t="n">
-        <v>3533.5</v>
+      <c r="H61" t="n">
+        <v>4255.3</v>
+      </c>
+      <c r="I61" t="n">
+        <v>3886.5</v>
+      </c>
+      <c r="J61" t="n">
+        <v>0</v>
+      </c>
+      <c r="K61" t="n">
+        <v>3886.5</v>
       </c>
     </row>
   </sheetData>
@@ -74195,13 +75120,13 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>3.877</v>
+        <v>3.817</v>
       </c>
       <c r="E8" t="n">
         <v>1.92</v>
       </c>
       <c r="F8" t="n">
-        <v>101.9</v>
+        <v>98.8</v>
       </c>
     </row>
     <row r="9">
@@ -74264,13 +75189,13 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>33.839</v>
+        <v>33.779</v>
       </c>
       <c r="E11" t="n">
         <v>32.22</v>
       </c>
       <c r="F11" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="12">
@@ -74429,13 +75354,13 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3.877</v>
+        <v>3.886</v>
       </c>
       <c r="E18" t="n">
         <v>1.99</v>
       </c>
       <c r="F18" t="n">
-        <v>94.8</v>
+        <v>95.3</v>
       </c>
     </row>
     <row r="19">
@@ -74498,7 +75423,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>35.99</v>
+        <v>35.999</v>
       </c>
       <c r="E21" t="n">
         <v>34.54</v>

--- a/output/Data and Chart Outputs/chile_power_capacity.xlsx
+++ b/output/Data and Chart Outputs/chile_power_capacity.xlsx
@@ -976,7 +976,7 @@
         <v>6.6399</v>
       </c>
       <c r="C2" t="n">
-        <v>8.5107</v>
+        <v>4.2553</v>
       </c>
       <c r="D2" t="n">
         <v>2.4784</v>
@@ -985,13 +985,13 @@
         <v>3.4343</v>
       </c>
       <c r="F2" t="n">
-        <v>6.8783</v>
+        <v>3.5165</v>
       </c>
       <c r="G2" t="n">
         <v>0.5157</v>
       </c>
       <c r="H2" t="n">
-        <v>8.887</v>
+        <v>5.3535</v>
       </c>
       <c r="I2" t="n">
         <v>0.1036</v>
@@ -1005,7 +1005,7 @@
         <v>6.6399</v>
       </c>
       <c r="C3" t="n">
-        <v>8.5107</v>
+        <v>4.2553</v>
       </c>
       <c r="D3" t="n">
         <v>2.6836</v>
@@ -1014,13 +1014,13 @@
         <v>3.5631</v>
       </c>
       <c r="F3" t="n">
-        <v>6.8869</v>
+        <v>3.5251</v>
       </c>
       <c r="G3" t="n">
         <v>0.5157</v>
       </c>
       <c r="H3" t="n">
-        <v>8.887</v>
+        <v>5.3535</v>
       </c>
       <c r="I3" t="n">
         <v>0.1036</v>
@@ -1034,7 +1034,7 @@
         <v>6.6399</v>
       </c>
       <c r="C4" t="n">
-        <v>8.5107</v>
+        <v>4.2553</v>
       </c>
       <c r="D4" t="n">
         <v>2.6836</v>
@@ -1043,13 +1043,13 @@
         <v>3.5657</v>
       </c>
       <c r="F4" t="n">
-        <v>6.8876</v>
+        <v>3.5258</v>
       </c>
       <c r="G4" t="n">
         <v>0.5157</v>
       </c>
       <c r="H4" t="n">
-        <v>8.887</v>
+        <v>5.3535</v>
       </c>
       <c r="I4" t="n">
         <v>0.1036</v>
@@ -1063,7 +1063,7 @@
         <v>6.6399</v>
       </c>
       <c r="C5" t="n">
-        <v>8.5107</v>
+        <v>4.2553</v>
       </c>
       <c r="D5" t="n">
         <v>2.6836</v>
@@ -1072,13 +1072,13 @@
         <v>3.8522</v>
       </c>
       <c r="F5" t="n">
-        <v>6.8876</v>
+        <v>3.5258</v>
       </c>
       <c r="G5" t="n">
         <v>0.5157</v>
       </c>
       <c r="H5" t="n">
-        <v>8.887</v>
+        <v>5.3535</v>
       </c>
       <c r="I5" t="n">
         <v>0.1036</v>
@@ -1092,7 +1092,7 @@
         <v>6.6624</v>
       </c>
       <c r="C6" t="n">
-        <v>8.5107</v>
+        <v>4.2553</v>
       </c>
       <c r="D6" t="n">
         <v>2.6836</v>
@@ -1101,13 +1101,13 @@
         <v>3.8822</v>
       </c>
       <c r="F6" t="n">
-        <v>6.8905</v>
+        <v>3.5287</v>
       </c>
       <c r="G6" t="n">
         <v>0.5157</v>
       </c>
       <c r="H6" t="n">
-        <v>8.887</v>
+        <v>5.3535</v>
       </c>
       <c r="I6" t="n">
         <v>0.1036</v>
@@ -1121,7 +1121,7 @@
         <v>6.6624</v>
       </c>
       <c r="C7" t="n">
-        <v>8.5107</v>
+        <v>4.2553</v>
       </c>
       <c r="D7" t="n">
         <v>2.7681</v>
@@ -1130,13 +1130,13 @@
         <v>4.1431</v>
       </c>
       <c r="F7" t="n">
-        <v>6.8995</v>
+        <v>3.5377</v>
       </c>
       <c r="G7" t="n">
         <v>0.5157</v>
       </c>
       <c r="H7" t="n">
-        <v>8.887</v>
+        <v>5.3535</v>
       </c>
       <c r="I7" t="n">
         <v>0.1036</v>
@@ -1150,7 +1150,7 @@
         <v>6.6624</v>
       </c>
       <c r="C8" t="n">
-        <v>8.5107</v>
+        <v>4.2553</v>
       </c>
       <c r="D8" t="n">
         <v>2.7681</v>
@@ -1159,13 +1159,13 @@
         <v>4.2572</v>
       </c>
       <c r="F8" t="n">
-        <v>6.9025</v>
+        <v>3.5407</v>
       </c>
       <c r="G8" t="n">
         <v>0.5157</v>
       </c>
       <c r="H8" t="n">
-        <v>8.887</v>
+        <v>5.3535</v>
       </c>
       <c r="I8" t="n">
         <v>0.1036</v>
@@ -1179,7 +1179,7 @@
         <v>6.6624</v>
       </c>
       <c r="C9" t="n">
-        <v>8.5107</v>
+        <v>4.2553</v>
       </c>
       <c r="D9" t="n">
         <v>2.7681</v>
@@ -1188,13 +1188,13 @@
         <v>4.434699999999999</v>
       </c>
       <c r="F9" t="n">
-        <v>7.0077</v>
+        <v>3.6459</v>
       </c>
       <c r="G9" t="n">
         <v>0.5157</v>
       </c>
       <c r="H9" t="n">
-        <v>8.887</v>
+        <v>5.3535</v>
       </c>
       <c r="I9" t="n">
         <v>0.1036</v>
@@ -1208,7 +1208,7 @@
         <v>6.6624</v>
       </c>
       <c r="C10" t="n">
-        <v>8.5107</v>
+        <v>4.2553</v>
       </c>
       <c r="D10" t="n">
         <v>2.8999</v>
@@ -1217,13 +1217,13 @@
         <v>4.583600000000001</v>
       </c>
       <c r="F10" t="n">
-        <v>7.0865</v>
+        <v>3.7247</v>
       </c>
       <c r="G10" t="n">
         <v>0.5187</v>
       </c>
       <c r="H10" t="n">
-        <v>8.887</v>
+        <v>5.3535</v>
       </c>
       <c r="I10" t="n">
         <v>0.1036</v>
@@ -1237,7 +1237,7 @@
         <v>6.6624</v>
       </c>
       <c r="C11" t="n">
-        <v>8.5107</v>
+        <v>4.2553</v>
       </c>
       <c r="D11" t="n">
         <v>3.0606</v>
@@ -1246,13 +1246,13 @@
         <v>4.6013</v>
       </c>
       <c r="F11" t="n">
-        <v>7.0865</v>
+        <v>3.7247</v>
       </c>
       <c r="G11" t="n">
         <v>0.5187</v>
       </c>
       <c r="H11" t="n">
-        <v>8.887</v>
+        <v>5.3535</v>
       </c>
       <c r="I11" t="n">
         <v>0.1036</v>
@@ -1266,7 +1266,7 @@
         <v>6.6624</v>
       </c>
       <c r="C12" t="n">
-        <v>8.5107</v>
+        <v>4.2553</v>
       </c>
       <c r="D12" t="n">
         <v>3.0606</v>
@@ -1275,13 +1275,13 @@
         <v>4.6123</v>
       </c>
       <c r="F12" t="n">
-        <v>7.0865</v>
+        <v>3.7247</v>
       </c>
       <c r="G12" t="n">
         <v>0.5187</v>
       </c>
       <c r="H12" t="n">
-        <v>8.887</v>
+        <v>5.3535</v>
       </c>
       <c r="I12" t="n">
         <v>0.1036</v>
@@ -3020,7 +3020,7 @@
         <v>6639.9</v>
       </c>
       <c r="C2" t="n">
-        <v>8510.700000000001</v>
+        <v>4255.3</v>
       </c>
       <c r="D2" t="n">
         <v>2478.4</v>
@@ -3029,13 +3029,13 @@
         <v>3434.3</v>
       </c>
       <c r="F2" t="n">
-        <v>8887</v>
+        <v>5353.5</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>6878.3</v>
+        <v>3516.5</v>
       </c>
       <c r="I2" t="n">
         <v>515.7</v>
@@ -3044,7 +3044,7 @@
         <v>103.6</v>
       </c>
       <c r="K2" t="n">
-        <v>37447.9</v>
+        <v>26297.2</v>
       </c>
     </row>
     <row r="3">
@@ -3055,7 +3055,7 @@
         <v>6639.9</v>
       </c>
       <c r="C3" t="n">
-        <v>8510.700000000001</v>
+        <v>4255.3</v>
       </c>
       <c r="D3" t="n">
         <v>2683.6</v>
@@ -3064,13 +3064,13 @@
         <v>3563.1</v>
       </c>
       <c r="F3" t="n">
-        <v>8887</v>
+        <v>5353.5</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>6886.9</v>
+        <v>3525.1</v>
       </c>
       <c r="I3" t="n">
         <v>515.7</v>
@@ -3079,7 +3079,7 @@
         <v>103.6</v>
       </c>
       <c r="K3" t="n">
-        <v>37790.5</v>
+        <v>26639.8</v>
       </c>
     </row>
     <row r="4">
@@ -3090,7 +3090,7 @@
         <v>6639.9</v>
       </c>
       <c r="C4" t="n">
-        <v>8510.700000000001</v>
+        <v>4255.3</v>
       </c>
       <c r="D4" t="n">
         <v>2683.6</v>
@@ -3099,13 +3099,13 @@
         <v>3565.7</v>
       </c>
       <c r="F4" t="n">
-        <v>8887</v>
+        <v>5353.5</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>6887.6</v>
+        <v>3525.8</v>
       </c>
       <c r="I4" t="n">
         <v>515.7</v>
@@ -3114,7 +3114,7 @@
         <v>103.6</v>
       </c>
       <c r="K4" t="n">
-        <v>37793.8</v>
+        <v>26643.1</v>
       </c>
     </row>
     <row r="5">
@@ -3125,7 +3125,7 @@
         <v>6639.9</v>
       </c>
       <c r="C5" t="n">
-        <v>8510.700000000001</v>
+        <v>4255.3</v>
       </c>
       <c r="D5" t="n">
         <v>2683.6</v>
@@ -3134,13 +3134,13 @@
         <v>3852.2</v>
       </c>
       <c r="F5" t="n">
-        <v>8887</v>
+        <v>5353.5</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>6887.6</v>
+        <v>3525.8</v>
       </c>
       <c r="I5" t="n">
         <v>515.7</v>
@@ -3149,7 +3149,7 @@
         <v>103.6</v>
       </c>
       <c r="K5" t="n">
-        <v>38080.3</v>
+        <v>26929.6</v>
       </c>
     </row>
     <row r="6">
@@ -3160,7 +3160,7 @@
         <v>6662.4</v>
       </c>
       <c r="C6" t="n">
-        <v>8510.700000000001</v>
+        <v>4255.3</v>
       </c>
       <c r="D6" t="n">
         <v>2683.6</v>
@@ -3169,13 +3169,13 @@
         <v>3882.2</v>
       </c>
       <c r="F6" t="n">
-        <v>8887</v>
+        <v>5353.5</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>6890.5</v>
+        <v>3528.7</v>
       </c>
       <c r="I6" t="n">
         <v>515.7</v>
@@ -3184,7 +3184,7 @@
         <v>103.6</v>
       </c>
       <c r="K6" t="n">
-        <v>38135.7</v>
+        <v>26985</v>
       </c>
     </row>
     <row r="7">
@@ -3195,7 +3195,7 @@
         <v>6662.4</v>
       </c>
       <c r="C7" t="n">
-        <v>8510.700000000001</v>
+        <v>4255.3</v>
       </c>
       <c r="D7" t="n">
         <v>2768.1</v>
@@ -3204,13 +3204,13 @@
         <v>4143.1</v>
       </c>
       <c r="F7" t="n">
-        <v>8887</v>
+        <v>5353.5</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>6899.5</v>
+        <v>3537.7</v>
       </c>
       <c r="I7" t="n">
         <v>515.7</v>
@@ -3219,7 +3219,7 @@
         <v>103.6</v>
       </c>
       <c r="K7" t="n">
-        <v>38490.1</v>
+        <v>27339.4</v>
       </c>
     </row>
     <row r="8">
@@ -3230,7 +3230,7 @@
         <v>6662.4</v>
       </c>
       <c r="C8" t="n">
-        <v>8510.700000000001</v>
+        <v>4255.3</v>
       </c>
       <c r="D8" t="n">
         <v>2768.1</v>
@@ -3239,13 +3239,13 @@
         <v>4257.2</v>
       </c>
       <c r="F8" t="n">
-        <v>8887</v>
+        <v>5353.5</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>6902.5</v>
+        <v>3540.7</v>
       </c>
       <c r="I8" t="n">
         <v>515.7</v>
@@ -3254,7 +3254,7 @@
         <v>103.6</v>
       </c>
       <c r="K8" t="n">
-        <v>38607.2</v>
+        <v>27456.5</v>
       </c>
     </row>
     <row r="9">
@@ -3265,7 +3265,7 @@
         <v>6662.4</v>
       </c>
       <c r="C9" t="n">
-        <v>8510.700000000001</v>
+        <v>4255.3</v>
       </c>
       <c r="D9" t="n">
         <v>2768.1</v>
@@ -3274,13 +3274,13 @@
         <v>4434.7</v>
       </c>
       <c r="F9" t="n">
-        <v>8887</v>
+        <v>5353.5</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>7007.7</v>
+        <v>3645.9</v>
       </c>
       <c r="I9" t="n">
         <v>515.7</v>
@@ -3289,7 +3289,7 @@
         <v>103.6</v>
       </c>
       <c r="K9" t="n">
-        <v>38889.9</v>
+        <v>27739.2</v>
       </c>
     </row>
     <row r="10">
@@ -3300,7 +3300,7 @@
         <v>6662.4</v>
       </c>
       <c r="C10" t="n">
-        <v>8510.700000000001</v>
+        <v>4255.3</v>
       </c>
       <c r="D10" t="n">
         <v>2899.9</v>
@@ -3309,13 +3309,13 @@
         <v>4583.6</v>
       </c>
       <c r="F10" t="n">
-        <v>8887</v>
+        <v>5353.5</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>7086.5</v>
+        <v>3724.7</v>
       </c>
       <c r="I10" t="n">
         <v>518.7</v>
@@ -3324,7 +3324,7 @@
         <v>103.6</v>
       </c>
       <c r="K10" t="n">
-        <v>39252.4</v>
+        <v>28101.7</v>
       </c>
     </row>
     <row r="11">
@@ -3335,7 +3335,7 @@
         <v>6662.4</v>
       </c>
       <c r="C11" t="n">
-        <v>8510.700000000001</v>
+        <v>4255.3</v>
       </c>
       <c r="D11" t="n">
         <v>3060.6</v>
@@ -3344,13 +3344,13 @@
         <v>4601.3</v>
       </c>
       <c r="F11" t="n">
-        <v>8887</v>
+        <v>5353.5</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>7086.5</v>
+        <v>3724.7</v>
       </c>
       <c r="I11" t="n">
         <v>518.7</v>
@@ -3359,7 +3359,7 @@
         <v>103.6</v>
       </c>
       <c r="K11" t="n">
-        <v>39430.8</v>
+        <v>28280.1</v>
       </c>
     </row>
     <row r="12">
@@ -3370,7 +3370,7 @@
         <v>6662.4</v>
       </c>
       <c r="C12" t="n">
-        <v>8510.700000000001</v>
+        <v>4255.3</v>
       </c>
       <c r="D12" t="n">
         <v>3060.6</v>
@@ -3379,13 +3379,13 @@
         <v>4612.3</v>
       </c>
       <c r="F12" t="n">
-        <v>8887</v>
+        <v>5353.5</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>7086.5</v>
+        <v>3724.7</v>
       </c>
       <c r="I12" t="n">
         <v>518.7</v>
@@ -3394,7 +3394,7 @@
         <v>103.6</v>
       </c>
       <c r="K12" t="n">
-        <v>39441.8</v>
+        <v>28291.1</v>
       </c>
     </row>
     <row r="13">
@@ -5474,28 +5474,28 @@
         <v>3533.5</v>
       </c>
       <c r="D2" t="n">
+        <v>1820</v>
+      </c>
+      <c r="E2" t="n">
         <v>5353.5</v>
-      </c>
-      <c r="E2" t="n">
-        <v>8887</v>
       </c>
       <c r="F2" t="n">
         <v>4255.3</v>
       </c>
       <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
         <v>4255.3</v>
-      </c>
-      <c r="H2" t="n">
-        <v>8510.700000000001</v>
       </c>
       <c r="I2" t="n">
         <v>3361.8</v>
       </c>
       <c r="J2" t="n">
+        <v>154.7</v>
+      </c>
+      <c r="K2" t="n">
         <v>3516.5</v>
-      </c>
-      <c r="K2" t="n">
-        <v>6878.3</v>
       </c>
     </row>
     <row r="3">
@@ -5509,28 +5509,28 @@
         <v>3533.5</v>
       </c>
       <c r="D3" t="n">
+        <v>1820</v>
+      </c>
+      <c r="E3" t="n">
         <v>5353.5</v>
-      </c>
-      <c r="E3" t="n">
-        <v>8887</v>
       </c>
       <c r="F3" t="n">
         <v>4255.3</v>
       </c>
       <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
         <v>4255.3</v>
-      </c>
-      <c r="H3" t="n">
-        <v>8510.700000000001</v>
       </c>
       <c r="I3" t="n">
         <v>3370.4</v>
       </c>
       <c r="J3" t="n">
-        <v>3516.5</v>
+        <v>154.7</v>
       </c>
       <c r="K3" t="n">
-        <v>6886.9</v>
+        <v>3525.1</v>
       </c>
     </row>
     <row r="4">
@@ -5544,28 +5544,28 @@
         <v>3533.5</v>
       </c>
       <c r="D4" t="n">
+        <v>1820</v>
+      </c>
+      <c r="E4" t="n">
         <v>5353.5</v>
-      </c>
-      <c r="E4" t="n">
-        <v>8887</v>
       </c>
       <c r="F4" t="n">
         <v>4255.3</v>
       </c>
       <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
         <v>4255.3</v>
-      </c>
-      <c r="H4" t="n">
-        <v>8510.700000000001</v>
       </c>
       <c r="I4" t="n">
         <v>3371.1</v>
       </c>
       <c r="J4" t="n">
-        <v>3516.5</v>
+        <v>154.7</v>
       </c>
       <c r="K4" t="n">
-        <v>6887.6</v>
+        <v>3525.8</v>
       </c>
     </row>
     <row r="5">
@@ -5579,28 +5579,28 @@
         <v>3533.5</v>
       </c>
       <c r="D5" t="n">
+        <v>1820</v>
+      </c>
+      <c r="E5" t="n">
         <v>5353.5</v>
-      </c>
-      <c r="E5" t="n">
-        <v>8887</v>
       </c>
       <c r="F5" t="n">
         <v>4255.3</v>
       </c>
       <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
         <v>4255.3</v>
-      </c>
-      <c r="H5" t="n">
-        <v>8510.700000000001</v>
       </c>
       <c r="I5" t="n">
         <v>3371.1</v>
       </c>
       <c r="J5" t="n">
-        <v>3516.5</v>
+        <v>154.7</v>
       </c>
       <c r="K5" t="n">
-        <v>6887.6</v>
+        <v>3525.8</v>
       </c>
     </row>
     <row r="6">
@@ -5614,28 +5614,28 @@
         <v>3533.5</v>
       </c>
       <c r="D6" t="n">
+        <v>1820</v>
+      </c>
+      <c r="E6" t="n">
         <v>5353.5</v>
-      </c>
-      <c r="E6" t="n">
-        <v>8887</v>
       </c>
       <c r="F6" t="n">
         <v>4255.3</v>
       </c>
       <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
         <v>4255.3</v>
-      </c>
-      <c r="H6" t="n">
-        <v>8510.700000000001</v>
       </c>
       <c r="I6" t="n">
         <v>3374</v>
       </c>
       <c r="J6" t="n">
-        <v>3516.5</v>
+        <v>154.7</v>
       </c>
       <c r="K6" t="n">
-        <v>6890.5</v>
+        <v>3528.7</v>
       </c>
     </row>
     <row r="7">
@@ -5649,28 +5649,28 @@
         <v>3533.5</v>
       </c>
       <c r="D7" t="n">
+        <v>1820</v>
+      </c>
+      <c r="E7" t="n">
         <v>5353.5</v>
-      </c>
-      <c r="E7" t="n">
-        <v>8887</v>
       </c>
       <c r="F7" t="n">
         <v>4255.3</v>
       </c>
       <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
         <v>4255.3</v>
-      </c>
-      <c r="H7" t="n">
-        <v>8510.700000000001</v>
       </c>
       <c r="I7" t="n">
         <v>3383</v>
       </c>
       <c r="J7" t="n">
-        <v>3516.5</v>
+        <v>154.7</v>
       </c>
       <c r="K7" t="n">
-        <v>6899.5</v>
+        <v>3537.7</v>
       </c>
     </row>
     <row r="8">
@@ -5684,28 +5684,28 @@
         <v>3533.5</v>
       </c>
       <c r="D8" t="n">
+        <v>1820</v>
+      </c>
+      <c r="E8" t="n">
         <v>5353.5</v>
-      </c>
-      <c r="E8" t="n">
-        <v>8887</v>
       </c>
       <c r="F8" t="n">
         <v>4255.3</v>
       </c>
       <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
         <v>4255.3</v>
-      </c>
-      <c r="H8" t="n">
-        <v>8510.700000000001</v>
       </c>
       <c r="I8" t="n">
         <v>3386</v>
       </c>
       <c r="J8" t="n">
-        <v>3516.5</v>
+        <v>154.7</v>
       </c>
       <c r="K8" t="n">
-        <v>6902.5</v>
+        <v>3540.7</v>
       </c>
     </row>
     <row r="9">
@@ -5719,28 +5719,28 @@
         <v>3533.5</v>
       </c>
       <c r="D9" t="n">
+        <v>1820</v>
+      </c>
+      <c r="E9" t="n">
         <v>5353.5</v>
-      </c>
-      <c r="E9" t="n">
-        <v>8887</v>
       </c>
       <c r="F9" t="n">
         <v>4255.3</v>
       </c>
       <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
         <v>4255.3</v>
-      </c>
-      <c r="H9" t="n">
-        <v>8510.700000000001</v>
       </c>
       <c r="I9" t="n">
         <v>3491.2</v>
       </c>
       <c r="J9" t="n">
-        <v>3516.5</v>
+        <v>154.7</v>
       </c>
       <c r="K9" t="n">
-        <v>7007.7</v>
+        <v>3645.9</v>
       </c>
     </row>
     <row r="10">
@@ -5754,28 +5754,28 @@
         <v>3533.5</v>
       </c>
       <c r="D10" t="n">
+        <v>1820</v>
+      </c>
+      <c r="E10" t="n">
         <v>5353.5</v>
-      </c>
-      <c r="E10" t="n">
-        <v>8887</v>
       </c>
       <c r="F10" t="n">
         <v>4255.3</v>
       </c>
       <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
         <v>4255.3</v>
-      </c>
-      <c r="H10" t="n">
-        <v>8510.700000000001</v>
       </c>
       <c r="I10" t="n">
         <v>3570</v>
       </c>
       <c r="J10" t="n">
-        <v>3516.5</v>
+        <v>154.7</v>
       </c>
       <c r="K10" t="n">
-        <v>7086.5</v>
+        <v>3724.7</v>
       </c>
     </row>
     <row r="11">
@@ -5789,28 +5789,28 @@
         <v>3533.5</v>
       </c>
       <c r="D11" t="n">
+        <v>1820</v>
+      </c>
+      <c r="E11" t="n">
         <v>5353.5</v>
-      </c>
-      <c r="E11" t="n">
-        <v>8887</v>
       </c>
       <c r="F11" t="n">
         <v>4255.3</v>
       </c>
       <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
         <v>4255.3</v>
-      </c>
-      <c r="H11" t="n">
-        <v>8510.700000000001</v>
       </c>
       <c r="I11" t="n">
         <v>3570</v>
       </c>
       <c r="J11" t="n">
-        <v>3516.5</v>
+        <v>154.7</v>
       </c>
       <c r="K11" t="n">
-        <v>7086.5</v>
+        <v>3724.7</v>
       </c>
     </row>
     <row r="12">
@@ -5824,28 +5824,28 @@
         <v>3533.5</v>
       </c>
       <c r="D12" t="n">
+        <v>1820</v>
+      </c>
+      <c r="E12" t="n">
         <v>5353.5</v>
-      </c>
-      <c r="E12" t="n">
-        <v>8887</v>
       </c>
       <c r="F12" t="n">
         <v>4255.3</v>
       </c>
       <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
         <v>4255.3</v>
-      </c>
-      <c r="H12" t="n">
-        <v>8510.700000000001</v>
       </c>
       <c r="I12" t="n">
         <v>3570</v>
       </c>
       <c r="J12" t="n">
-        <v>3516.5</v>
+        <v>154.7</v>
       </c>
       <c r="K12" t="n">
-        <v>7086.5</v>
+        <v>3724.7</v>
       </c>
     </row>
     <row r="13">

--- a/output/Data and Chart Outputs/chile_power_capacity.xlsx
+++ b/output/Data and Chart Outputs/chile_power_capacity.xlsx
@@ -26,8 +26,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="166" formatCode="mmm/yy"/>
+    <numFmt numFmtId="165" formatCode="mmm/yy"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -67,12 +67,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -823,7 +824,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
@@ -845,7 +845,6 @@
         </is>
       </c>
     </row>
-    <row r="8"/>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
@@ -860,7 +859,6 @@
         </is>
       </c>
     </row>
-    <row r="11"/>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
@@ -889,7 +887,6 @@
         </is>
       </c>
     </row>
-    <row r="16"/>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
@@ -969,7 +966,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="n">
+      <c r="A2" s="5" t="n">
         <v>44197</v>
       </c>
       <c r="B2" t="n">
@@ -998,7 +995,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="n">
+      <c r="A3" s="5" t="n">
         <v>44228</v>
       </c>
       <c r="B3" t="n">
@@ -1027,7 +1024,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="n">
+      <c r="A4" s="5" t="n">
         <v>44256</v>
       </c>
       <c r="B4" t="n">
@@ -1056,7 +1053,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="n">
+      <c r="A5" s="5" t="n">
         <v>44287</v>
       </c>
       <c r="B5" t="n">
@@ -1085,7 +1082,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="n">
+      <c r="A6" s="5" t="n">
         <v>44317</v>
       </c>
       <c r="B6" t="n">
@@ -1114,7 +1111,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="n">
+      <c r="A7" s="5" t="n">
         <v>44348</v>
       </c>
       <c r="B7" t="n">
@@ -1143,7 +1140,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="n">
+      <c r="A8" s="5" t="n">
         <v>44378</v>
       </c>
       <c r="B8" t="n">
@@ -1172,7 +1169,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="n">
+      <c r="A9" s="5" t="n">
         <v>44409</v>
       </c>
       <c r="B9" t="n">
@@ -1201,7 +1198,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="n">
+      <c r="A10" s="5" t="n">
         <v>44440</v>
       </c>
       <c r="B10" t="n">
@@ -1230,7 +1227,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="n">
+      <c r="A11" s="5" t="n">
         <v>44470</v>
       </c>
       <c r="B11" t="n">
@@ -1259,7 +1256,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="n">
+      <c r="A12" s="5" t="n">
         <v>44501</v>
       </c>
       <c r="B12" t="n">
@@ -1288,7 +1285,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="n">
+      <c r="A13" s="5" t="n">
         <v>44531</v>
       </c>
       <c r="B13" t="n">
@@ -1317,7 +1314,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="n">
+      <c r="A14" s="5" t="n">
         <v>44562</v>
       </c>
       <c r="B14" t="n">
@@ -1346,7 +1343,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="n">
+      <c r="A15" s="5" t="n">
         <v>44593</v>
       </c>
       <c r="B15" t="n">
@@ -1375,7 +1372,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="n">
+      <c r="A16" s="5" t="n">
         <v>44621</v>
       </c>
       <c r="B16" t="n">
@@ -1404,7 +1401,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="n">
+      <c r="A17" s="5" t="n">
         <v>44652</v>
       </c>
       <c r="B17" t="n">
@@ -1433,7 +1430,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="n">
+      <c r="A18" s="5" t="n">
         <v>44682</v>
       </c>
       <c r="B18" t="n">
@@ -1462,7 +1459,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="n">
+      <c r="A19" s="5" t="n">
         <v>44713</v>
       </c>
       <c r="B19" t="n">
@@ -1491,7 +1488,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="n">
+      <c r="A20" s="5" t="n">
         <v>44743</v>
       </c>
       <c r="B20" t="n">
@@ -1520,7 +1517,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="n">
+      <c r="A21" s="5" t="n">
         <v>44774</v>
       </c>
       <c r="B21" t="n">
@@ -1549,7 +1546,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="n">
+      <c r="A22" s="5" t="n">
         <v>44805</v>
       </c>
       <c r="B22" t="n">
@@ -1578,7 +1575,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="n">
+      <c r="A23" s="5" t="n">
         <v>44835</v>
       </c>
       <c r="B23" t="n">
@@ -1607,7 +1604,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="n">
+      <c r="A24" s="5" t="n">
         <v>44866</v>
       </c>
       <c r="B24" t="n">
@@ -1636,7 +1633,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="n">
+      <c r="A25" s="5" t="n">
         <v>44896</v>
       </c>
       <c r="B25" t="n">
@@ -1665,7 +1662,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="n">
+      <c r="A26" s="5" t="n">
         <v>44927</v>
       </c>
       <c r="B26" t="n">
@@ -1694,7 +1691,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="n">
+      <c r="A27" s="5" t="n">
         <v>44958</v>
       </c>
       <c r="B27" t="n">
@@ -1723,7 +1720,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="n">
+      <c r="A28" s="5" t="n">
         <v>44986</v>
       </c>
       <c r="B28" t="n">
@@ -1752,7 +1749,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="n">
+      <c r="A29" s="5" t="n">
         <v>45017</v>
       </c>
       <c r="B29" t="n">
@@ -1781,7 +1778,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="3" t="n">
+      <c r="A30" s="5" t="n">
         <v>45047</v>
       </c>
       <c r="B30" t="n">
@@ -1810,7 +1807,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="3" t="n">
+      <c r="A31" s="5" t="n">
         <v>45078</v>
       </c>
       <c r="B31" t="n">
@@ -1839,7 +1836,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="3" t="n">
+      <c r="A32" s="5" t="n">
         <v>45108</v>
       </c>
       <c r="B32" t="n">
@@ -1868,7 +1865,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="3" t="n">
+      <c r="A33" s="5" t="n">
         <v>45139</v>
       </c>
       <c r="B33" t="n">
@@ -1897,7 +1894,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="3" t="n">
+      <c r="A34" s="5" t="n">
         <v>45170</v>
       </c>
       <c r="B34" t="n">
@@ -1926,7 +1923,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="3" t="n">
+      <c r="A35" s="5" t="n">
         <v>45200</v>
       </c>
       <c r="B35" t="n">
@@ -1955,7 +1952,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="3" t="n">
+      <c r="A36" s="5" t="n">
         <v>45231</v>
       </c>
       <c r="B36" t="n">
@@ -1984,7 +1981,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="3" t="n">
+      <c r="A37" s="5" t="n">
         <v>45261</v>
       </c>
       <c r="B37" t="n">
@@ -2013,7 +2010,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="3" t="n">
+      <c r="A38" s="5" t="n">
         <v>45292</v>
       </c>
       <c r="B38" t="n">
@@ -2042,7 +2039,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="3" t="n">
+      <c r="A39" s="5" t="n">
         <v>45323</v>
       </c>
       <c r="B39" t="n">
@@ -2071,7 +2068,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="3" t="n">
+      <c r="A40" s="5" t="n">
         <v>45352</v>
       </c>
       <c r="B40" t="n">
@@ -2100,7 +2097,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="3" t="n">
+      <c r="A41" s="5" t="n">
         <v>45383</v>
       </c>
       <c r="B41" t="n">
@@ -2129,7 +2126,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="3" t="n">
+      <c r="A42" s="5" t="n">
         <v>45413</v>
       </c>
       <c r="B42" t="n">
@@ -2158,7 +2155,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="3" t="n">
+      <c r="A43" s="5" t="n">
         <v>45444</v>
       </c>
       <c r="B43" t="n">
@@ -2187,7 +2184,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="3" t="n">
+      <c r="A44" s="5" t="n">
         <v>45474</v>
       </c>
       <c r="B44" t="n">
@@ -2216,7 +2213,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="3" t="n">
+      <c r="A45" s="5" t="n">
         <v>45505</v>
       </c>
       <c r="B45" t="n">
@@ -2245,7 +2242,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="3" t="n">
+      <c r="A46" s="5" t="n">
         <v>45536</v>
       </c>
       <c r="B46" t="n">
@@ -2274,7 +2271,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="3" t="n">
+      <c r="A47" s="5" t="n">
         <v>45566</v>
       </c>
       <c r="B47" t="n">
@@ -2303,7 +2300,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="3" t="n">
+      <c r="A48" s="5" t="n">
         <v>45597</v>
       </c>
       <c r="B48" t="n">
@@ -2332,7 +2329,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="3" t="n">
+      <c r="A49" s="5" t="n">
         <v>45627</v>
       </c>
       <c r="B49" t="n">
@@ -2361,7 +2358,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="3" t="n">
+      <c r="A50" s="5" t="n">
         <v>45658</v>
       </c>
       <c r="B50" t="n">
@@ -2390,7 +2387,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="3" t="n">
+      <c r="A51" s="5" t="n">
         <v>45689</v>
       </c>
       <c r="B51" t="n">
@@ -2419,7 +2416,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="3" t="n">
+      <c r="A52" s="5" t="n">
         <v>45717</v>
       </c>
       <c r="B52" t="n">
@@ -2448,7 +2445,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="3" t="n">
+      <c r="A53" s="5" t="n">
         <v>45748</v>
       </c>
       <c r="B53" t="n">
@@ -2477,7 +2474,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="3" t="n">
+      <c r="A54" s="5" t="n">
         <v>45778</v>
       </c>
       <c r="B54" t="n">
@@ -2506,7 +2503,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="3" t="n">
+      <c r="A55" s="5" t="n">
         <v>45809</v>
       </c>
       <c r="B55" t="n">
@@ -2535,7 +2532,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="3" t="n">
+      <c r="A56" s="5" t="n">
         <v>45839</v>
       </c>
       <c r="B56" t="n">
@@ -2564,7 +2561,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="3" t="n">
+      <c r="A57" s="5" t="n">
         <v>45870</v>
       </c>
       <c r="B57" t="n">
@@ -2593,7 +2590,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="3" t="n">
+      <c r="A58" s="5" t="n">
         <v>45901</v>
       </c>
       <c r="B58" t="n">
@@ -2622,7 +2619,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="3" t="n">
+      <c r="A59" s="5" t="n">
         <v>45931</v>
       </c>
       <c r="B59" t="n">
@@ -2651,7 +2648,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="3" t="n">
+      <c r="A60" s="5" t="n">
         <v>45962</v>
       </c>
       <c r="B60" t="n">
@@ -2680,7 +2677,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="3" t="n">
+      <c r="A61" s="5" t="n">
         <v>45992</v>
       </c>
       <c r="B61" t="n">
@@ -2709,7 +2706,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="3" t="n">
+      <c r="A62" s="5" t="n">
         <v>46023</v>
       </c>
       <c r="B62" t="n">
@@ -2738,7 +2735,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="3" t="n">
+      <c r="A63" s="5" t="n">
         <v>46054</v>
       </c>
       <c r="B63" t="n">
@@ -2767,7 +2764,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="3" t="n">
+      <c r="A64" s="5" t="n">
         <v>46082</v>
       </c>
       <c r="B64" t="n">
@@ -2796,7 +2793,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="3" t="n">
+      <c r="A65" s="5" t="n">
         <v>46113</v>
       </c>
       <c r="B65" t="n">
@@ -2825,7 +2822,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="3" t="n">
+      <c r="A66" s="5" t="n">
         <v>46143</v>
       </c>
       <c r="B66" t="n">
@@ -2854,7 +2851,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="3" t="n">
+      <c r="A67" s="5" t="n">
         <v>46174</v>
       </c>
       <c r="B67" t="n">
@@ -2883,7 +2880,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="3" t="n">
+      <c r="A68" s="5" t="n">
         <v>46204</v>
       </c>
       <c r="B68" t="n">
@@ -2912,7 +2909,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="3" t="n">
+      <c r="A69" s="5" t="n">
         <v>46235</v>
       </c>
       <c r="B69" t="n">

--- a/output/Data and Chart Outputs/chile_power_capacity.xlsx
+++ b/output/Data and Chart Outputs/chile_power_capacity.xlsx
@@ -162,6 +162,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:rPr sz="1200" b="1"/>
               <a:t>Chile installed generation capacity (CNE) (to Aug/26)</a:t>
             </a:r>
           </a:p>
@@ -295,7 +296,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="E87BA4"/>
+              <a:srgbClr val="6E4B2A"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -323,7 +324,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="008300"/>
+              <a:srgbClr val="8A9A2B"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -351,7 +352,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="4A3AA7"/>
+              <a:srgbClr val="E87BA4"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -379,7 +380,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="E34948"/>
+              <a:srgbClr val="008300"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
